--- a/atlas-weekly.xlsx
+++ b/atlas-weekly.xlsx
@@ -149,7 +149,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -159,7 +159,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18T20:21:35</t>
+          <t xml:space="preserve">2026-10-20T13:00:04</t>
         </is>
       </c>
     </row>
@@ -228,7 +228,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-12</t>
+          <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
     </row>
@@ -240,7 +240,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
     </row>
@@ -252,7 +252,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-19T09:00:21</t>
+          <t xml:space="preserve">2026-10-20T13:00:16</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4847,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G10"/>
   <cols>
     <col min="1" max="1" width="12"/>
     <col min="2" max="2" width="17"/>
@@ -4898,7 +4898,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4908,49 +4908,49 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magic mushroom ingredient takes the fight out of aggressive fish</t>
+          <t xml:space="preserve">Scientists find a way to fight Alzheimer’s brain damage without removing toxic tau</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A psychedelic compound found in magic mushrooms appears to have an unexpected effect: calming highly aggressive fish. Researchers discovered that low doses of psilocybin significantly reduced aggressive attacks in mangrove rivulus fish without disrupting their normal social interactions. The findings suggest psilocybin may selectively calm escalating aggression rather than simply suppressing all behavior.</t>
+          <t xml:space="preserve">Scientists have found a promising way to protect the brain from Alzheimer’s-related damage by blocking immune cells that contribute to the destruction of neurons. In mice, the treatment preserved roughly 40% more tissue in memory centers and improved memory, even without removing harmful tau protein buildup.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Small molecule</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261017230036.htm</t>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261019093355.htm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ScienceDaily</t>
+          <t xml:space="preserve">The Transmitter</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientists find a youth protein that helps aging brain cells act young again</t>
+          <t xml:space="preserve">COVID-19 and influenza effects in pregnancy; and more</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientists have discovered that a protein linked to youth helps protect the brain’s immune cells from age-related decline. Restoring the protein in older mice improved the cells’ ability to clear debris and reduced signs of inflammation, raising hopes for future treatments targeting brain aging and Alzheimer’s disease.</t>
+          <t xml:space="preserve">Here is a roundup of autism-related news and research spotted around the web for the week of 19 October.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4960,34 +4960,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261016070646.htm</t>
+          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/covid-19-and-influenza-effects-in-pregnancy-and-more/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-16</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Transmitter</t>
+          <t xml:space="preserve">ScienceDaily</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Highly cited autism paper earns expression of concern over data duplications</t>
+          <t xml:space="preserve">Why some people escape Alzheimer’s despite carrying a high-risk gene</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">The notice, published in Nature last week, also addressed an image duplication identified by a prominent research-integrity sleuth.</t>
+          <t xml:space="preserve">Scientists have discovered why some people with a high genetic risk of Alzheimer’s remain mentally sharp into their 80s, uncovering a rare mutation that protects the brain from harmful protein buildup. The findings reveal a potential new way to prevent early brain damage and could pave the way for treatments that mimic this natural defense.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4997,19 +4997,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/highly-cited-autism-paper-earns-expression-of-concern-over-data-duplications/</t>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261018205044.htm</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5019,49 +5019,49 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rare study reveals a striking divide inside an Alzheimer’s patient’s brain</t>
+          <t xml:space="preserve">Magic mushroom ingredient takes the fight out of aggressive fish</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A rare examination of an Alzheimer’s patient’s brain revealed that regions cleared of amyloid plaques had remarkably little of the harmful tau buildup associated with memory loss, while neighboring areas showed extensive damage. The discovery suggests that removing amyloid may have lasting protective effects and could help slow Alzheimer’s progression, especially when treatment begins early.</t>
+          <t xml:space="preserve">A psychedelic compound found in magic mushrooms appears to have an unexpected effect: calming highly aggressive fish. Researchers discovered that low doses of psilocybin significantly reduced aggressive attacks in mangrove rivulus fish without disrupting their normal social interactions. The findings suggest psilocybin may selectively calm escalating aggression rather than simply suppressing all behavior.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Small molecule</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261013015814.htm</t>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261017230036.htm</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Transmitter</t>
+          <t xml:space="preserve">ScienceDaily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acetaminophen effects on developing brain organoids; and more</t>
+          <t xml:space="preserve">Scientists find a youth protein that helps aging brain cells act young again</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Here is a roundup of autism-related news and research spotted around the web for the week of 12 October.</t>
+          <t xml:space="preserve">Scientists have discovered that a protein linked to youth helps protect the brain’s immune cells from age-related decline. Restoring the protein in older mice improved the cells’ ability to clear debris and reduced signs of inflammation, raising hopes for future treatments targeting brain aging and Alzheimer’s disease.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5071,54 +5071,165 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/acetaminophen-effects-on-developing-brain-organoids-and-more/</t>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261016070646.htm</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-10-16</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Transmitter</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Highly cited autism paper earns expression of concern over data duplications</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The notice, published in Nature last week, also addressed an image duplication identified by a prominent research-integrity sleuth.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/highly-cited-autism-paper-earns-expression-of-concern-over-data-duplications/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ScienceDaily</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rare study reveals a striking divide inside an Alzheimer’s patient’s brain</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A rare examination of an Alzheimer’s patient’s brain revealed that regions cleared of amyloid plaques had remarkably little of the harmful tau buildup associated with memory loss, while neighboring areas showed extensive damage. The discovery suggests that removing amyloid may have lasting protective effects and could help slow Alzheimer’s progression, especially when treatment begins early.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261013015814.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t xml:space="preserve">The Transmitter</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Acetaminophen effects on developing brain organoids; and more</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Here is a roundup of autism-related news and research spotted around the web for the week of 12 October.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/acetaminophen-effects-on-developing-brain-organoids-and-more/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-13</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Transmitter</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">Private initiative makes ‘historic’ investment in autism research</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t xml:space="preserve">Aligning Research to Impact Autism has committed more than $450 million to build a new multidisciplinary research network to uncover the roots of profound autism and develop treatments.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-15</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.thetransmitter.org/spectrum/private-initiative-makes-historic-investment-in-autism-research/</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G10"/>
 </worksheet>
 </file>
 

--- a/atlas-weekly.xlsx
+++ b/atlas-weekly.xlsx
@@ -105,7 +105,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -115,7 +115,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
     </row>
@@ -149,7 +149,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -159,7 +159,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20T13:00:04</t>
+          <t xml:space="preserve">2026-10-24T08:57:28</t>
         </is>
       </c>
     </row>
@@ -181,7 +181,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
     </row>
@@ -193,7 +193,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -203,7 +203,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
     </row>
@@ -228,7 +228,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
     </row>
@@ -240,7 +240,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
     </row>
@@ -252,7 +252,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20T13:00:16</t>
+          <t xml:space="preserve">2026-10-24T08:58:52</t>
         </is>
       </c>
     </row>
@@ -274,19 +274,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q41"/>
   <cols>
     <col min="1" max="1" width="12"/>
     <col min="2" max="2" width="16"/>
-    <col min="3" max="3" width="20"/>
-    <col min="4" max="4" width="16"/>
-    <col min="5" max="5" width="53"/>
+    <col min="3" max="3" width="18"/>
+    <col min="4" max="4" width="18"/>
+    <col min="5" max="5" width="63"/>
     <col min="6" max="6" width="70"/>
     <col min="7" max="7" width="15"/>
     <col min="8" max="8" width="25"/>
     <col min="9" max="9" width="17"/>
     <col min="10" max="10" width="28"/>
-    <col min="11" max="11" width="54"/>
+    <col min="11" max="11" width="25"/>
     <col min="12" max="12" width="22"/>
     <col min="13" max="13" width="10"/>
     <col min="14" max="14" width="10"/>
@@ -385,27 +385,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-07</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verosky BG</t>
+          <t xml:space="preserve">Li H</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gur TL</t>
+          <t xml:space="preserve">Xu B</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verosky BG, Chen HJ, Anderson JL, et al.</t>
+          <t xml:space="preserve">Li H, Choi JJ, Huang EJ, et al.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -430,17 +430,17 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cytokines &amp; Inflammation</t>
+          <t xml:space="preserve">Genetics &amp; Molecular</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Intervention &amp; Clinical</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t xml:space="preserve">translational</t>
+          <t xml:space="preserve">mechanistic</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -450,17 +450,17 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t xml:space="preserve">42844313</t>
+          <t xml:space="preserve">42892634</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prenatal stress reprograms placental signaling and opposes maternal immune activation effects in the fetal brain.</t>
+          <t xml:space="preserve">A microglial basis for fragile X syndrome via impairment of FMRP-regulated lysosomal function.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42844313/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42892634/</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -472,37 +472,37 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan P</t>
+          <t xml:space="preserve">Lack O</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Waddington H</t>
+          <t xml:space="preserve">Simonoff E</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jordan P, Tupou J, Hammond M, et al.</t>
+          <t xml:space="preserve">Lack O, Hollocks MJ, Baird G, et al.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Autism</t>
+          <t xml:space="preserve">Autism Research</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.5</t>
+          <t xml:space="preserve">5.2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -512,7 +512,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177</t>
+          <t xml:space="preserve">133</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">unclassified</t>
+          <t xml:space="preserve">clinical-observation</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -537,17 +537,17 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42872382</t>
+          <t xml:space="preserve">42919820</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commentary: A Neurodiversity-Affirming Framework for Evaluating Autism Support Research.</t>
+          <t xml:space="preserve">Psychological and Neurodevelopmental Correlates of Extreme Demand Avoidance in a Clinical Sample, an Exploratory Study.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42872382/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42919820/</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -559,37 +559,37 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">O'Reilly Sparks KC</t>
+          <t xml:space="preserve">Cola M</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pedapati EV</t>
+          <t xml:space="preserve">Parish-Morris J</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">O'Reilly Sparks KC, Pedapati EV</t>
+          <t xml:space="preserve">Cola M, Lyons M, Schillinger S, et al.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biological Psychiatry</t>
+          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">3.2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">301</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -609,12 +609,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t xml:space="preserve">review</t>
+          <t xml:space="preserve">unclassified</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -624,17 +624,17 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t xml:space="preserve">42869120</t>
+          <t xml:space="preserve">42911481</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neural Circuits of Social Behavior in Autism Spectrum Disorder: From Mechanism to Intervention.</t>
+          <t xml:space="preserve">Context Matters: Assessing Sex and Diagnostic Differences in Autistic Children's Language Across Tasks With Differing Levels of Structure.</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42869120/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42911481/</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -646,27 +646,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wu QF</t>
+          <t xml:space="preserve">Edwards G</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du JQ</t>
+          <t xml:space="preserve">Waite J</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wu QF, Du JQ</t>
+          <t xml:space="preserve">Edwards G, Tarver J, Mingins JE, et al.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -691,17 +691,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Intervention &amp; Clinical</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-trial</t>
+          <t xml:space="preserve">clinical-observation</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">42867737</t>
+          <t xml:space="preserve">42911479</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enhancing Attention and Executive Function in Children With Autism Spectrum Disorder: A Randomized Controlled Trial of a 12-Week Multimodal Art Intervention.</t>
+          <t xml:space="preserve">Correlates of Anxiety in Children and Adults With Moderate to Profound Intellectual Disability.</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42867737/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42911479/</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -733,27 +733,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-12</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dunham-Carr K</t>
+          <t xml:space="preserve">Russell A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Woynaroski TG</t>
+          <t xml:space="preserve">Melia R</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dunham-Carr K, Feldman JI, Simon DM, et al.</t>
+          <t xml:space="preserve">Russell A, Cremen C, Kirby A, et al.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -798,17 +798,17 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t xml:space="preserve">42862433</t>
+          <t xml:space="preserve">42911478</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scalp Topography of Event-Related Potentials Reveals Differences in Audiovisual Speech Processing in Autistic and Non-Autistic Children.</t>
+          <t xml:space="preserve">Experiences of Suicide Prevention Interventions and Supports for Autistic Adults: Perspectives of Autistic Adults, Family Members and Clinicians.</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42862433/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42911478/</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -820,37 +820,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-12</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mishra A</t>
+          <t xml:space="preserve">Kawakami S</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scott L</t>
+          <t xml:space="preserve">Otsuka S</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mishra A, Wang J, Scott L</t>
+          <t xml:space="preserve">Kawakami S, Uono S, Murai T, et al.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
+          <t xml:space="preserve">Autism Research</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.2</t>
+          <t xml:space="preserve">5.2</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t xml:space="preserve">301</t>
+          <t xml:space="preserve">133</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-observation</t>
+          <t xml:space="preserve">unclassified</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t xml:space="preserve">42862432</t>
+          <t xml:space="preserve">42897683</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enhancing Peer-Directed Social Communication in Autistic Children Using Video Visual Scene Displays.</t>
+          <t xml:space="preserve">The Japanese Adaptation of the Reading the Mind in Films Test: Differentiating Autism Spectrum Disorder From Depression Using an Ecologically Valid Social Cognitive Task.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42862432/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42897683/</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -907,37 +907,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-11</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chen F</t>
+          <t xml:space="preserve">Pemberton E</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weng C</t>
+          <t xml:space="preserve">Fox JRE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chen F, Kneifati-Hayek J, Zelin C, et al.</t>
+          <t xml:space="preserve">Pemberton E, Milne E, Fox JRE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Autism Research</t>
+          <t xml:space="preserve">Autism</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2</t>
+          <t xml:space="preserve">7.5</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">133</t>
+          <t xml:space="preserve">177</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intervention &amp; Clinical</t>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-observation</t>
+          <t xml:space="preserve">unclassified</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t xml:space="preserve">42860767</t>
+          <t xml:space="preserve">42888939</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Characterizing Autism Phenotype Onset in the Electronic Health Records to Enable Age-Specific Screening.</t>
+          <t xml:space="preserve">Why Do You Think You're More Likely to be Queer? Exploring Autistic Perspectives on the Intersection Between Autism and Sexual Minority Identities.</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42860767/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42888939/</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -994,17 +994,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-08</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Swanepoel A</t>
+          <t xml:space="preserve">Sukhodolsky DG</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1014,17 +1014,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Swanepoel A</t>
+          <t xml:space="preserve">Sukhodolsky DG</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Journal of Child Psychology and Psychiatry</t>
+          <t xml:space="preserve">Journal of the American Academy of Child &amp; Adolescent Psychiatry</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.2</t>
+          <t xml:space="preserve">9.2</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1034,12 +1034,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">345</t>
+          <t xml:space="preserve">359</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intervention &amp; Clinical</t>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t xml:space="preserve">mechanistic</t>
+          <t xml:space="preserve">other</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t xml:space="preserve">42849904</t>
+          <t xml:space="preserve">42887673</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Editorial Perspective: Evolutionary psychiatry as a scientific framework for neurodiversity: implications for ADHD and ASD in children and young people.</t>
+          <t xml:space="preserve">Editorial: Sensory Features and Restricted and Repetitive Behaviors in Autism Spectrum Disorder.</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42849904/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42887673/</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1081,27 +1081,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-08</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hegarty JP</t>
+          <t xml:space="preserve">Cuni E</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hardan AY</t>
+          <t xml:space="preserve">Cantero-García M</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hegarty JP, Komaki H, Gu M, et al.</t>
+          <t xml:space="preserve">Cuni E, Cantero-García M</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t xml:space="preserve">unclassified</t>
+          <t xml:space="preserve">review</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t xml:space="preserve">42848294</t>
+          <t xml:space="preserve">42886452</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cerebellar Crus I and Crus II Structure and Excitation/Inhibition Balance in Autism Spectrum Disorder.</t>
+          <t xml:space="preserve">Autistic Masking and Mental Health Outcomes in Autistic Women: A Systematic Review (2015-2025).</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42848294/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42886452/</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1168,37 +1168,37 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-07</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cullingham T</t>
+          <t xml:space="preserve">Wohofsky L</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Green J</t>
+          <t xml:space="preserve">Krainer D</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cullingham T, Larkin M, Milton D, et al.</t>
+          <t xml:space="preserve">Wohofsky L, Küffner C, Fink SH, et al.</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Autism</t>
+          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.5</t>
+          <t xml:space="preserve">3.2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve">177</t>
+          <t xml:space="preserve">301</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t xml:space="preserve">unclassified</t>
+          <t xml:space="preserve">clinical-observation</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1233,17 +1233,17 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t xml:space="preserve">42844592</t>
+          <t xml:space="preserve">42886451</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anxiety Problems Experienced by Autistic Children: Child and Parent Perspectives.</t>
+          <t xml:space="preserve">Development of Autism-Inclusive Approaches for Everyday Life in a Participatory Process: From Challenges to Resolutions.</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42844592/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42886451/</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1255,37 +1255,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parada GE</t>
+          <t xml:space="preserve">Lim A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Blencowe BJ</t>
+          <t xml:space="preserve">Brewer N</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parada GE, Bretschneider H, Li JD, et al.</t>
+          <t xml:space="preserve">Lim A, Brewer N</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nature</t>
+          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">50.5</t>
+          <t xml:space="preserve">3.2</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849</t>
+          <t xml:space="preserve">301</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genetics &amp; Molecular</t>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Intervention &amp; Clinical</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">unclassified</t>
+          <t xml:space="preserve">clinical-observation</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1320,17 +1320,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t xml:space="preserve">42875502</t>
+          <t xml:space="preserve">42886448</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">A microexon regulatory code reveals autism-linked genetic variation.</t>
+          <t xml:space="preserve">Cyber Dependent Crime May Be Predicted by Autism Diagnosis but Not Autistic Traits.</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42875502/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42886448/</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1342,37 +1342,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korkmaz S</t>
+          <t xml:space="preserve">Flores J</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bourgeron T</t>
+          <t xml:space="preserve">Zimic M</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korkmaz S, De Sainte Agathe JM, Cliquet F, et al.</t>
+          <t xml:space="preserve">Flores J, Montero AE, Barrientos F, et al.</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biological Psychiatry</t>
+          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">3.2</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">301</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1392,12 +1392,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genetics &amp; Molecular, Neuroscience &amp; Imaging</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t xml:space="preserve">review</t>
+          <t xml:space="preserve">unclassified</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1407,17 +1407,17 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t xml:space="preserve">42854861</t>
+          <t xml:space="preserve">42886447</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t xml:space="preserve">The genetic orchestra of autism and its intersections with epilepsy, intellectual disability, and ADHD.</t>
+          <t xml:space="preserve">Analysis of the Pupillary Light Reflex Response Against Light Stimuli for Autism Screening in Children.</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42854861/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42886447/</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1429,37 +1429,37 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starnawska A</t>
+          <t xml:space="preserve">Han JE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demontis D</t>
+          <t xml:space="preserve">Kim SH</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Starnawska A, Nielsen TT, Grove J, et al.</t>
+          <t xml:space="preserve">Han JE, Shin Y, Elias R, et al.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biological Psychiatry</t>
+          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">9.0</t>
+          <t xml:space="preserve">3.2</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve">431</t>
+          <t xml:space="preserve">301</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-observation</t>
+          <t xml:space="preserve">unclassified</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1494,17 +1494,17 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t xml:space="preserve">42869119</t>
+          <t xml:space="preserve">42881350</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genetic architecture and risk of suicide attempt across neurodevelopmental and psychiatric conditions.</t>
+          <t xml:space="preserve">Comparing Intervention Outcome Measures Across Clinic and Home for Young Autistic Children: Brief Observation of Social Communication Change (BOSCC) and Measure of NDBI Strategy Implementation-Caregiver Change (MONSI-CC).</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42869119/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42881350/</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1516,37 +1516,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-10</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuntzner-Gibson K</t>
+          <t xml:space="preserve">Liao C</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geng Y</t>
+          <t xml:space="preserve">Neale BM</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stuntzner-Gibson K, Zhang P, He B, et al.</t>
+          <t xml:space="preserve">Liao C, Ye R, Ivankovic F, et al.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular Psychiatry</t>
+          <t xml:space="preserve">Nature Genetics</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.0</t>
+          <t xml:space="preserve">29.0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve">320</t>
+          <t xml:space="preserve">788</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1581,17 +1581,17 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t xml:space="preserve">42859211</t>
+          <t xml:space="preserve">42901987</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zebrafish behavioral phenomics reveals functional subtypes of autism risk genes.</t>
+          <t xml:space="preserve">The landscape of gene loss and missense variation across the mammalian tree informs on gene essentiality.</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42859211/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42901987/</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1603,37 +1603,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meyer-Schuman R</t>
+          <t xml:space="preserve">Hao Y</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zoghbi H</t>
+          <t xml:space="preserve">Troyanskaya OG</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meyer-Schuman R, Cherry F, Sui Y, et al.</t>
+          <t xml:space="preserve">Hao Y, Park CY, Theesfeld CL, et al.</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">American Journal of Human Genetics</t>
+          <t xml:space="preserve">Nature Neuroscience</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.1</t>
+          <t xml:space="preserve">21.2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">390</t>
+          <t xml:space="preserve">605</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t xml:space="preserve">Genetics &amp; Molecular</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t xml:space="preserve">unclassified</t>
+          <t xml:space="preserve">clinical-observation</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1668,17 +1668,17 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t xml:space="preserve">42854690</t>
+          <t xml:space="preserve">42881222</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">A massively parallel reporter assay of MECP2cis-regulatory elements reveals genetic candidates for male-biased autism.</t>
+          <t xml:space="preserve">Spatiotemporal AI-based modeling of gene regulation and variant effects in the developing human brain using Seal.</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42854690/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42881222/</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1690,37 +1690,37 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esgin Ö</t>
+          <t xml:space="preserve">Findling RL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hamitoglu A</t>
+          <t xml:space="preserve">Smith E</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Esgin Ö, Ari-Arat C, Yilmaz G, et al.</t>
+          <t xml:space="preserve">Findling RL, Bozhdaraj D, Duffy W, et al.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
+          <t xml:space="preserve">Journal of the American Academy of Child &amp; Adolescent Psychiatry</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.2</t>
+          <t xml:space="preserve">9.2</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve">301</t>
+          <t xml:space="preserve">359</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intervention &amp; Clinical</t>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-observation</t>
+          <t xml:space="preserve">clinical-trial</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">42867738</t>
+          <t xml:space="preserve">42914007</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Comparison of Eating Behaviours, Anthropometric Measures, and Malnutrition Risk in Children With Autism Spectrum Disorder and Other Developmental Disabilities.</t>
+          <t xml:space="preserve">Cariprazine in the Treatment of Pediatric Patients With Irritability Associated With Autism Spectrum Disorder: A Randomized Controlled Trial.</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42867738/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42914007/</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1777,27 +1777,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-12</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crehan E</t>
+          <t xml:space="preserve">Parenteau CI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loftin R</t>
+          <t xml:space="preserve">Lerner MD</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crehan E, Whaling K, Jones H, et al.</t>
+          <t xml:space="preserve">Parenteau CI, Nahmias AS, Lerner MD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-observation</t>
+          <t xml:space="preserve">clinical-trial</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1842,17 +1842,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t xml:space="preserve">42862434</t>
+          <t xml:space="preserve">42911480</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diagnostic Agreement of a Structured Telehealth Adult Autism Assessment.</t>
+          <t xml:space="preserve">Feasibility, Acceptability, and Efficacy of an Ecological Momentary Intervention for Autistic Adults.</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42862434/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42911480/</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1864,37 +1864,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-12</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Robinette LM</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Keim SA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">N/A</t>
+          <t xml:space="preserve">Robinette LM, Taylor HG, Boone KM, et al.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Autism Research</t>
+          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2</t>
+          <t xml:space="preserve">3.2</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">133</t>
+          <t xml:space="preserve">301</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1929,17 +1929,17 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t xml:space="preserve">42861636</t>
+          <t xml:space="preserve">42911477</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Correction to "Effects of Cannabidiol on Social Relating, Anxiety, and Parental Stress in Autistic Children: A Randomized Controlled Crossover Trial".</t>
+          <t xml:space="preserve">Fatty Acid Supplementation in Toddlers Born Preterm and Attention and Autism Outcomes at 8-10 Years: Omega Tots Randomized Controlled Trial Long-Term Follow-Up.</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42861636/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42911477/</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1951,37 +1951,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-10</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rankins EM</t>
+          <t xml:space="preserve">Ren C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peters BC</t>
+          <t xml:space="preserve">Peng K</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rankins EM, Aichele S, Granger DA, et al.</t>
+          <t xml:space="preserve">Ren C, Zhang Q, Liang X, et al.</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
+          <t xml:space="preserve">Autism Research</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.2</t>
+          <t xml:space="preserve">5.2</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">301</t>
+          <t xml:space="preserve">133</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-trial</t>
+          <t xml:space="preserve">unclassified</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2016,17 +2016,17 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t xml:space="preserve">42859339</t>
+          <t xml:space="preserve">42885320</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Effects of Incorporating Horses into Occupational Therapy on Adrenocortical and Sympathetic Nervous System Reactivity and Regulation in Autistic Children: A Randomized Controlled Trial.</t>
+          <t xml:space="preserve">Establishing Diagnosis Models for Autism Spectrum Disorder With Auditory Brainstem Response Using Machine Learning Methods.</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42859339/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42885320/</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2038,37 +2038,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-08</t>
+          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cross K</t>
+          <t xml:space="preserve">Johnson N</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">James AI</t>
+          <t xml:space="preserve">Koth K</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cross K, Knott F, James AI</t>
+          <t xml:space="preserve">Johnson N, Van Hecke A, Hine J, et al.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Autism</t>
+          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.5</t>
+          <t xml:space="preserve">3.2</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve">177</t>
+          <t xml:space="preserve">301</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2103,17 +2103,17 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t xml:space="preserve">42851035</t>
+          <t xml:space="preserve">42879056</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Invisible Needs and Uneven Recognition: A National FOI Study of Autism Support Across Diagnostic Stages in U.K. Universities.</t>
+          <t xml:space="preserve">Battling the Bottleneck: Evaluating Autism Diagnostic Training in Primary Care.</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42851035/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42879056/</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2125,52 +2125,52 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramaekers VT</t>
+          <t xml:space="preserve">Chau KH</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quadros EV</t>
+          <t xml:space="preserve">LaSalle JM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ramaekers VT, Quadros EV</t>
+          <t xml:space="preserve">Chau KH, LaSalle JM</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biochimie</t>
+          <t xml:space="preserve">Current topics in behavioral neurosciences</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">203</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neuroimmunology</t>
+          <t xml:space="preserve">Genetics &amp; Molecular</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t xml:space="preserve">review</t>
+          <t xml:space="preserve">clinical-observation</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2190,17 +2190,17 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t xml:space="preserve">42874702</t>
+          <t xml:space="preserve">42888366</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Evolving Paradigm of Autism: Folate Receptor Autoimmunity deranging Epigenetic Programming in fetal and postnatal Brain Development.</t>
+          <t xml:space="preserve">Modifiers of Genetics in ASD Etiology.</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42874702/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42888366/</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -2217,32 +2217,32 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjørklund G</t>
+          <t xml:space="preserve">Sönmezler E</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Oktay Y</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjørklund G</t>
+          <t xml:space="preserve">Sönmezler E, Hız Kurul S, Erez O, et al.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular neurobiology</t>
+          <t xml:space="preserve">Human molecular genetics</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5</t>
+          <t xml:space="preserve">3.2</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve">176</t>
+          <t xml:space="preserve">357</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neuroimmunology</t>
+          <t xml:space="preserve">Genetics &amp; Molecular</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t xml:space="preserve">review</t>
+          <t xml:space="preserve">translational</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2277,17 +2277,17 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t xml:space="preserve">42867752</t>
+          <t xml:space="preserve">42905887</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metallothionein-Related Findings in Autism Spectrum Disorder: A Systematic Review and Targeted Quantitative Synthesis of Human Studies.</t>
+          <t xml:space="preserve">KATNAL2 dysfunction impairs microtubule dynamics and contributes to syndromic neurodevelopmental disease.</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42867752/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42905887/</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -2299,62 +2299,62 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-02</t>
+          <t xml:space="preserve">2026-10-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hata N</t>
+          <t xml:space="preserve">Popov TN</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matsuzaki H</t>
+          <t xml:space="preserve">Vachev TI</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hata N, Hirai T, Umeda N, et al.</t>
+          <t xml:space="preserve">Popov TN, Minchev SD, Vachev TI</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Journal of psychiatric research</t>
+          <t xml:space="preserve">Balkan journal of medical genetics : BJMG</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.6</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve">220</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental</t>
+          <t xml:space="preserve">Genetics &amp; Molecular</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cytokines &amp; Inflammation</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-observation</t>
+          <t xml:space="preserve">translational</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2364,17 +2364,17 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t xml:space="preserve">42843280</t>
+          <t xml:space="preserve">42877398</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Association of soluble epoxide hydrolase in neonatal cord blood with symptoms of autism spectrum disorder: Hamamatsu Birth Cohort for Mothers and Children (HBC Study).</t>
+          <t xml:space="preserve">Identification of Peripheral Blood mIR-128-3p Molecular Signature in Children with Autism Spectrum Disorder.</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42843280/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42877398/</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -2386,37 +2386,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-07</t>
+          <t xml:space="preserve">2026-07-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhong S</t>
+          <t xml:space="preserve">Elangovan A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Happé F</t>
+          <t xml:space="preserve">Vellingiri B</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhong S, Jones K, Knight KF, et al.</t>
+          <t xml:space="preserve">Elangovan A, Roy A, Karuppusamy PA, et al.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neuropsychologia</t>
+          <t xml:space="preserve">Behavioural brain research</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5</t>
+          <t xml:space="preserve">3.0</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2426,12 +2426,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t xml:space="preserve">322</t>
+          <t xml:space="preserve">252</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental</t>
+          <t xml:space="preserve">Genetics &amp; Molecular</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-observation</t>
+          <t xml:space="preserve">review</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2451,17 +2451,17 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t xml:space="preserve">42413861</t>
+          <t xml:space="preserve">42480870</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exploring the experiences of autistic and non-autistic aphantasics: A qualitative study.</t>
+          <t xml:space="preserve">Non-coding RNA dysregulation in autism spectrum disorder: Mechanisms, biomarkers, and therapeutic perspectives.</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42413861/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42480870/</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -2473,62 +2473,62 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sim J</t>
+          <t xml:space="preserve">Aldurayhim F</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lee DH</t>
+          <t xml:space="preserve">Pringsheim T</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sim J, Choi KS, Lee DH</t>
+          <t xml:space="preserve">Aldurayhim F, Martino D, Sarna JR, et al.</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">JMIR research protocols</t>
+          <t xml:space="preserve">Movement disorders clinical practice</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental</t>
+          <t xml:space="preserve">Intervention &amp; Clinical</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intervention &amp; Clinical</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-trial</t>
+          <t xml:space="preserve">clinical-observation</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2538,17 +2538,17 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t xml:space="preserve">42852593</t>
+          <t xml:space="preserve">42902960</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Exploring the Neural Mechanisms of Acupuncture Stimulation in Autism Spectrum Disorder: Protocol for a Randomized, Sham-Controlled, Multimodal Neuroimaging Trial.</t>
+          <t xml:space="preserve">When Tics and Autism Meet: Phenomenology, Severity, and Treatment Patterns.</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42852593/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42902960/</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -2560,52 +2560,52 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-12</t>
+          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y I Baamer M</t>
+          <t xml:space="preserve">Roychowdhury B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Santhosh VN</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Y I Baamer M</t>
+          <t xml:space="preserve">Roychowdhury B, Jalihal S, Ankola AV, et al.</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Applied neuropsychology. Adult</t>
+          <t xml:space="preserve">Journal of the American Dental Association (1939)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve">51</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental</t>
+          <t xml:space="preserve">Intervention &amp; Clinical</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t xml:space="preserve">unclassified</t>
+          <t xml:space="preserve">clinical-trial</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">42860913</t>
+          <t xml:space="preserve">42886150</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Associations between executive function and core symptoms of attention-deficit/hyperactivity disorder in adults with autism spectrum disorder: Controlling for theory of mind, and age.</t>
+          <t xml:space="preserve">Comparative effectiveness of triple-headed and conventional toothbrushes for plaque control and gingival health in children and adolescents with autism spectrum disorder: A randomized controlled trial.</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42860913/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42886150/</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -2647,32 +2647,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-10</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moyses-Oliveira M</t>
+          <t xml:space="preserve">Bonnot O</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Talkowski ME</t>
+          <t xml:space="preserve">Gollier-Briant F</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moyses-Oliveira M, Liu Y, Erdin S, et al.</t>
+          <t xml:space="preserve">Bonnot O, Mouhoud T, Shadili G, et al.</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">HGG advances</t>
+          <t xml:space="preserve">L'Encephale</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genetics &amp; Molecular</t>
+          <t xml:space="preserve">Intervention &amp; Clinical</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t xml:space="preserve">translational</t>
+          <t xml:space="preserve">clinical-trial</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t xml:space="preserve">42433021</t>
+          <t xml:space="preserve">42907297</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t xml:space="preserve">CRISPR-engineered deletion of POGZ alters transcription factor binding at promoters of genes involved in synaptic signaling.</t>
+          <t xml:space="preserve">[Artificial intelligence in child and adolescent psychiatry: A critical review of uses, evidence and relational stakes].</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42433021/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42907297/</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -2734,32 +2734,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-10</t>
+          <t xml:space="preserve">2026-10-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geng C</t>
+          <t xml:space="preserve">Dallman AR</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Xie H</t>
+          <t xml:space="preserve">Jimenez ME</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Geng C, Shangguan S, Chen X, et al.</t>
+          <t xml:space="preserve">Dallman AR, Santucci G, Lai D, et al.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhonghua yi xue yi chuan xue za zhi = Zhonghua yixue yichuanxue zazhi = Chinese journal of medical genetics</t>
+          <t xml:space="preserve">The American journal of occupational therapy : official publication of the American Occupational Therapy Association</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genetics &amp; Molecular</t>
+          <t xml:space="preserve">Intervention &amp; Clinical</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2799,17 +2799,17 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t xml:space="preserve">42711128</t>
+          <t xml:space="preserve">42862150</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Genetic and phenotypic analysis of three children with Neurodevelopmental disorders due to variants of DEAF1 gene].</t>
+          <t xml:space="preserve">Lifestyle Documentation in Therapy Evaluations for Autistic Children: A Lexicon-Based Analysis of Electronic Health Records.</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42711128/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42862150/</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
@@ -2821,52 +2821,52 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-01</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kılıçaslan F</t>
+          <t xml:space="preserve">Peng S</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gürler Aİ</t>
+          <t xml:space="preserve">Liu R</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kılıçaslan F, Öz Ö, Carık C, et al.</t>
+          <t xml:space="preserve">Peng S, Wang L, Ouyang J, et al.</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Developmental neurobiology</t>
+          <t xml:space="preserve">MedComm</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.0</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve">100</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genetics &amp; Molecular</t>
+          <t xml:space="preserve">Neuroimmunology</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-observation</t>
+          <t xml:space="preserve">review</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2886,17 +2886,17 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t xml:space="preserve">42876007</t>
+          <t xml:space="preserve">42898978</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syndromic Autism in Helsmoortel-Van der Aa Syndrome: From Clinical Suspicion to Genetic Diagnosis.</t>
+          <t xml:space="preserve">The Role of Astrocytes in the Inflammatory Response in Neurodiseases.</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42876007/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42898978/</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
@@ -2908,37 +2908,37 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-07</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jahandideh P</t>
+          <t xml:space="preserve">Khusenova N</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bitaraf A</t>
+          <t xml:space="preserve">Abramyan A</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jahandideh P, Bitaraf A</t>
+          <t xml:space="preserve">Khusenova N, Madjidova Y, Mizamov F, et al.</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Molecular neurobiology</t>
+          <t xml:space="preserve">Brain &amp; development</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.5</t>
+          <t xml:space="preserve">1.4</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2948,12 +2948,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">176</t>
+          <t xml:space="preserve">121</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genetics &amp; Molecular</t>
+          <t xml:space="preserve">Cytokines &amp; Inflammation</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t xml:space="preserve">review</t>
+          <t xml:space="preserve">clinical-observation</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2973,17 +2973,17 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t xml:space="preserve">42842117</t>
+          <t xml:space="preserve">42914764</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pathological Priming and Developmental Heterochrony as Organizing Concepts in Human iPSC Models of Autism Spectrum Disorder.</t>
+          <t xml:space="preserve">Clinical, immunological and metabolic features and gut-brain axis markers in children with autism spectrum disorder and TORCH-associated central nervous system involvement.</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42842117/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42914764/</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
@@ -2995,37 +2995,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bertoni G</t>
+          <t xml:space="preserve">Li A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Menna E</t>
+          <t xml:space="preserve">Xiao Y</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bertoni G, Rossi A, Colapietro P, et al.</t>
+          <t xml:space="preserve">Li A, Zhang J, Yu C, et al.</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pharmacological research</t>
+          <t xml:space="preserve">Psychiatry research</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.2</t>
+          <t xml:space="preserve">4.6</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t xml:space="preserve">220</t>
+          <t xml:space="preserve">249</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cytokines &amp; Inflammation</t>
+          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t xml:space="preserve">translational</t>
+          <t xml:space="preserve">clinical-observation</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t xml:space="preserve">42869260</t>
+          <t xml:space="preserve">42892189</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prenatal exposure to maternal SARS-CoV-2 infection leads to altered neuro-immune biomarker profiles at birth.</t>
+          <t xml:space="preserve">Predicting individual differences in social functioning from functional connectomes in children with autism spectrum disorder.</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42869260/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42892189/</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
@@ -3082,52 +3082,52 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-26</t>
+          <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ko MY</t>
+          <t xml:space="preserve">Li X</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ka M</t>
+          <t xml:space="preserve">Cao F</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ko MY, Min E, Hyun SA, et al.</t>
+          <t xml:space="preserve">Li X, Zuo F, Cheng Y, et al.</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Behavioural brain research</t>
+          <t xml:space="preserve">Proceedings of the National Academy of Sciences of the United States of America</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.0</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">252</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cytokines &amp; Inflammation</t>
+          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t xml:space="preserve">review</t>
+          <t xml:space="preserve">clinical-observation</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t xml:space="preserve">42361859</t>
+          <t xml:space="preserve">42879491</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impact of per- and polyfluoroalkyl substances (PFAS) on brain development and function.</t>
+          <t xml:space="preserve">Two clusters of brain regions with distinct age-related profiles of functional connectivity in autism spectrum disorder.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42361859/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42879491/</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
@@ -3169,52 +3169,52 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-14</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">De Chiara S</t>
+          <t xml:space="preserve">Li Y</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Di Lorenzo F</t>
+          <t xml:space="preserve">Li R</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">De Chiara S, Di Somma A, Mazziotti V, et al.</t>
+          <t xml:space="preserve">Li Y, Zhang L, Hou L, et al.</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chembiochem : a European journal of chemical biology</t>
+          <t xml:space="preserve">IEEE transactions on bio-medical engineering</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.9</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">162</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cytokines &amp; Inflammation</t>
+          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t xml:space="preserve">mechanistic</t>
+          <t xml:space="preserve">clinical-observation</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3234,17 +3234,17 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t xml:space="preserve">42809586</t>
+          <t xml:space="preserve">42911835</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Functional Heterogeneity of the Autism Spectrum Disorder-Associated Gut Microbial Ecosystem Revealed by Fecal Lipopolysaccharides and Bacterial Proteomic Profiling.</t>
+          <t xml:space="preserve">Multimodal Analysis of Brain Network Abnormalities in Autism Spectrum Disorder: a Graph Neural Network-based Fusion Investigation of EEG and fNIRS.</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42809586/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42911835/</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
@@ -3256,27 +3256,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-25</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gibula-Tarlowska E</t>
+          <t xml:space="preserve">Bakul F</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kotlinska JH</t>
+          <t xml:space="preserve">Kana RK</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gibula-Tarlowska E, Grochecki P, Lubinska J, et al.</t>
+          <t xml:space="preserve">Bakul F, Krafick KI, Kana RK</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cytokines &amp; Inflammation</t>
+          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t xml:space="preserve">mechanistic</t>
+          <t xml:space="preserve">review</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t xml:space="preserve">42501761</t>
+          <t xml:space="preserve">42918308</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Effects of early postnatal dopamine transporter (DAT) inhibition on social and cognitive behavior in a rat model of autism.</t>
+          <t xml:space="preserve">The Spectrum within the Spectrum: Neural Heterogeneity in Autism.</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42501761/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42918308/</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
@@ -3343,52 +3343,52 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-08</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">M S SP</t>
+          <t xml:space="preserve">Bory P</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">A ST</t>
+          <t xml:space="preserve">Denis A</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">M S SP, A ST</t>
+          <t xml:space="preserve">Bory P, Fiorentino M, Bérenguier L, et al.</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cognitive neurodynamics</t>
+          <t xml:space="preserve">L'Encephale</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.9</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">70</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-observation</t>
+          <t xml:space="preserve">review</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t xml:space="preserve">42857201</t>
+          <t xml:space="preserve">42888159</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t xml:space="preserve">A geometric rs-fMRI connectome descriptor reveals individual stability without robust autism group differences.</t>
+          <t xml:space="preserve">Autistic burnout: Early insights from a systematic review on characteristics, precipitating factors, and protective mechanisms.</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42857201/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42888159/</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
@@ -3430,52 +3430,52 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-07</t>
+          <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yan C</t>
+          <t xml:space="preserve">Kang S</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ao L</t>
+          <t xml:space="preserve">Locke J</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yan C, Zhu G, Liang S, et al.</t>
+          <t xml:space="preserve">Kang S, Ghosh Choudhuri P, Sridhar A, et al.</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">International medical case reports journal</t>
+          <t xml:space="preserve">Autism</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.6</t>
+          <t xml:space="preserve">7.5</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
+          <t xml:space="preserve">JCR impact factor</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">26</t>
+          <t xml:space="preserve">177</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3485,7 +3485,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-observation</t>
+          <t xml:space="preserve">unclassified</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3495,17 +3495,17 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t xml:space="preserve">42865690</t>
+          <t xml:space="preserve">42888940</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Feasibility and Safety of Transcranial Focused Ultrasound on Language Impairment in a Patient with Autism Spectrum Disorder: A Case Report.</t>
+          <t xml:space="preserve">"Our Principal Makes It Happen": The Role of Implementation Leadership in Supporting Evidence-Based Practices With Autistic Children in Inclusive Settings.</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42865690/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42888940/</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
@@ -3517,52 +3517,52 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ren H</t>
+          <t xml:space="preserve">Morgan PL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liu C</t>
+          <t xml:space="preserve">Hu EH</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ren H, Duan Y, Li H, et al.</t>
+          <t xml:space="preserve">Morgan PL, Hu EH</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brain imaging and behavior</t>
+          <t xml:space="preserve">Autism</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3</t>
+          <t xml:space="preserve">7.5</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
+          <t xml:space="preserve">JCR impact factor</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">89</t>
+          <t xml:space="preserve">177</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-observation</t>
+          <t xml:space="preserve">unclassified</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3582,17 +3582,17 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t xml:space="preserve">42853485</t>
+          <t xml:space="preserve">42885509</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gray matter subtyping with SuStaIn reveals neuroanatomical patterns in autism spectrum disorder.</t>
+          <t xml:space="preserve">Intersectional Disparities in School-Based Autism Identification Are Occurring in U.S. Elementary Schools.</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42853485/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42885509/</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
@@ -3604,52 +3604,52 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-07</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liang S</t>
+          <t xml:space="preserve">Aguado-Gracia J</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gu F</t>
+          <t xml:space="preserve">Calvo Escalona R</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liang S, Zhang Z, Du W, et al.</t>
+          <t xml:space="preserve">Aguado-Gracia J, Borràs R, Calvo Escalona R</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biomedical physics &amp; engineering express</t>
+          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.7</t>
+          <t xml:space="preserve">3.2</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
+          <t xml:space="preserve">JCR impact factor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">42</t>
+          <t xml:space="preserve">301</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t xml:space="preserve">unclassified</t>
+          <t xml:space="preserve">other</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3669,17 +3669,17 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t xml:space="preserve">42843381</t>
+          <t xml:space="preserve">42909748</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t xml:space="preserve">A multi-atlas ensemble learning framework for autism spectrum disorder diagnosis.</t>
+          <t xml:space="preserve">Correction to: Differential Associations of Adversity and Victimisation With Psychotic Experiences in Autistic Adolescents.</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42843381/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42909748/</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
@@ -3691,52 +3691,52 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-07</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suman P</t>
+          <t xml:space="preserve">Babalola TT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prajapati J</t>
+          <t xml:space="preserve">Botting N</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suman P, Kaur J, Pal S, et al.</t>
+          <t xml:space="preserve">Babalola TT, Moss R, Dipper L, et al.</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Journal of developmental and behavioral pediatrics : JDBP</t>
+          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4</t>
+          <t xml:space="preserve">3.2</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
+          <t xml:space="preserve">JCR impact factor</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">168</t>
+          <t xml:space="preserve">301</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intervention &amp; Clinical</t>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-trial</t>
+          <t xml:space="preserve">unclassified</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3756,17 +3756,17 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t xml:space="preserve">42841398</t>
+          <t xml:space="preserve">42909747</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Effectiveness of Parent-mediated Intervention Versus Standard Therapist-based Intervention in Indian Children With Autism Spectrum Disorder: A Randomized Controlled Trial.</t>
+          <t xml:space="preserve">Understanding Healthcare Access for Autistic Children in the UK: Perspectives From Parents and Healthcare Professionals.</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42841398/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42909747/</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
@@ -3778,62 +3778,62 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-09</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anchan V</t>
+          <t xml:space="preserve">Cardelle-Pérez F</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Srikanth N</t>
+          <t xml:space="preserve">Leal-Hernández M</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anchan V, C T, Sahoo S, et al.</t>
+          <t xml:space="preserve">Cardelle-Pérez F, Banacloig-Delgado C, Muros-Cobos NI, et al.</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">JMIR research protocols</t>
+          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6</t>
+          <t xml:space="preserve">3.2</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
+          <t xml:space="preserve">JCR impact factor</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">62</t>
+          <t xml:space="preserve">301</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intervention &amp; Clinical</t>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental, Cytokines &amp; Inflammation</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t xml:space="preserve">clinical-trial</t>
+          <t xml:space="preserve">clinical-observation</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3843,17 +3843,17 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t xml:space="preserve">42854201</t>
+          <t xml:space="preserve">42909746</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multidimensional Evaluation of the Efficacy of a Comprehensive Ayurveda Approach as an Add-On to Conventional Therapy in Children With Autism Spectrum Disorder: Protocol for a Randomized, Open-Label, Parallel-Group, Active-Controlled Clinical Trial.</t>
+          <t xml:space="preserve">Brief Report: User Participation in the Iterative Co-Design of Public Child Mental Health Services.</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42854201/</t>
+          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42909746/</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
@@ -3862,878 +3862,8 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-08</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kemp E</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crasta J</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kemp E, Yates S, Quincy L, et al.</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The American journal of occupational therapy : official publication of the American Occupational Therapy Association</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intervention &amp; Clinical</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinical-trial</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42847600</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Treatment Fidelity of AquOTic: An Occupational Therapy-Based Aquatic Intervention for Children on the Autism Spectrum.</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42847600/</t>
-        </is>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-07-22</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Otsuka S</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Murai T</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Otsuka S, Oe S, Yamada S, et al.</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Psychiatry and clinical neurosciences</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2.6</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intervention &amp; Clinical</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinical-trial</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42487254</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Different effects of social cognitive skills training in schizophrenia and autism spectrum disorder: A rater-blinded, multicenter, randomized controlled trial.</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42487254/</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-14</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wu Z</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Li F</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wu Z, Pu Y, Zhou W, et al.</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autism</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.5</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JCR impact factor</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinical-observation</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42872383</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Disparities in Social Determinants of Health and Health Outcomes Among Autistic Individuals Without Intellectual Disability in Middle-to-Late Adulthood.</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42872383/</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-09</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Giannakopoulos G</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Papanikolaou K</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Giannakopoulos G, Martinos MM, Ntre V, et al.</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autism</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.5</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JCR impact factor</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unclassified</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42852941</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autistic Young Adults' Experiences of Support and Participation in Postsecondary Education in Greece.</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42852941/</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-07</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Girolamo T</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Suhrheinrich J</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Girolamo T, Rivera D, Greene-Pendelton K, et al.</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autism</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.5</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JCR impact factor</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">other</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42844649</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"It Is Awful for Your Morale": A Need for Person-Centered Approaches to Speech-Language Services for Autistic Young Adults.</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42844649/</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-10</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wood JJ</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Crowell SE</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wood JJ, Orm S, Wood KS, et al.</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Journal of Child Psychology and Psychiatry</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7.2</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JCR impact factor</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">345</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Intervention &amp; Clinical</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unclassified</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42856069</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The emotion regulation and recognition account of empathy-related processes in autism: a multimodal, multilevel case-control study.</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42856069/</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-08</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ho LC</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wei LC</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ho LC, Wei LC</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autism Research</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5.2</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JCR impact factor</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">other</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42850942</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Social Anxiety Should be a Routine, Autistic-Led Treatment Target.</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42850942/</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-12</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wu Z</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">To CKS</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Wu Z, To CKS</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.2</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JCR impact factor</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">301</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unclassified</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42862435</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Challenges in Accommodating Talker Variability in Lexical Tone Perception Among Autistic Adults: Implications for Talker Adaptation.</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42862435/</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-07</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chua SJS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Henry JD</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Chua SJS, Terrett G, Coundouris SP, et al.</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.2</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JCR impact factor</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">301</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">unclassified</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42842175</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The Functional Application of Episodic Foresight in Autistic Children.</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42842175/</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-07</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agyapong M</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">STAARS Team</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agyapong M, Mason L, Begum Ali J, et al.</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3.2</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JCR impact factor</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">301</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">clinical-observation</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42842174</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Infant Attention to Eyes Versus Mouth Varies With Mouth Movement Speed, Family History of Autism and Language Development.</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42842174/</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:Q51"/>
+  <autoFilter ref="A1:Q41"/>
 </worksheet>
 </file>
 
@@ -4847,7 +3977,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <cols>
     <col min="1" max="1" width="12"/>
     <col min="2" max="2" width="17"/>
@@ -4898,7 +4028,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4908,12 +4038,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientists find a way to fight Alzheimer’s brain damage without removing toxic tau</t>
+          <t xml:space="preserve">Scientists discover a hidden messaging system deep inside the brain</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientists have found a promising way to protect the brain from Alzheimer’s-related damage by blocking immune cells that contribute to the destruction of neurons. In mice, the treatment preserved roughly 40% more tissue in memory centers and improved memory, even without removing harmful tau protein buildup.</t>
+          <t xml:space="preserve">A tiny region deep within the brain has surprised scientists by revealing a remarkably sophisticated communication system. Previously thought to broadcast the same chemical signal throughout the brain, this region actually sends targeted messages that help control learning, attention, and behavior, according to new research in mice.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4923,34 +4053,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261019093355.htm</t>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261022081304.htm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Transmitter</t>
+          <t xml:space="preserve">ScienceDaily</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">COVID-19 and influenza effects in pregnancy; and more</t>
+          <t xml:space="preserve">Scientists discover a surprising secret behind the human brain’s wrinkles</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Here is a roundup of autism-related news and research spotted around the web for the week of 19 October.</t>
+          <t xml:space="preserve">Scientists have discovered why common marmosets have unusually small, smooth brains despite starting development much like other primates. The secret lies in subtle changes to brain-building cells that slow neuron production, revealing new clues about how the large, folded human brain evolved.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4960,34 +4090,34 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/covid-19-and-influenza-effects-in-pregnancy-and-more/</t>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261021231235.htm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ScienceDaily</t>
+          <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Why some people escape Alzheimer’s despite carrying a high-risk gene</t>
+          <t xml:space="preserve">Depression profile linked to disrupted sleep and poorer treatment responses</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientists have discovered why some people with a high genetic risk of Alzheimer’s remain mentally sharp into their 80s, uncovering a rare mutation that protects the brain from harmful protein buildup. The findings reveal a potential new way to prevent early brain damage and could pave the way for treatments that mimic this natural defense.</t>
+          <t xml:space="preserve">This study uncovers a circadian depression subtype, revealing links between sleep patterns, symptom severity, and antidepressant response in a large cohort.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4997,71 +4127,71 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261018205044.htm</t>
+          <t xml:space="preserve">https://www.news-medical.net/news/20261022/Depression-profile-linked-to-disrupted-sleep-and-poorer-treatment-responses.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ScienceDaily</t>
+          <t xml:space="preserve">The Transmitter</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Magic mushroom ingredient takes the fight out of aggressive fish</t>
+          <t xml:space="preserve">Prevalence of profound autism declines with new definition</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">A psychedelic compound found in magic mushrooms appears to have an unexpected effect: calming highly aggressive fish. Researchers discovered that low doses of psilocybin significantly reduced aggressive attacks in mangrove rivulus fish without disrupting their normal social interactions. The findings suggest psilocybin may selectively calm escalating aggression rather than simply suppressing all behavior.</t>
+          <t xml:space="preserve">The updated, more precise definition used in a CDC study includes adaptive scores.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Small molecule</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261017230036.htm</t>
+          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/prevalence-of-profound-autism-declines-with-new-definition/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ScienceDaily</t>
+          <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientists find a youth protein that helps aging brain cells act young again</t>
+          <t xml:space="preserve">Global study aims to map brain changes across eight psychiatric disorders</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientists have discovered that a protein linked to youth helps protect the brain’s immune cells from age-related decline. Restoring the protein in older mice improved the cells’ ability to clear debris and reduced signs of inflammation, raising hopes for future treatments targeting brain aging and Alzheimer’s disease.</t>
+          <t xml:space="preserve">Researchers from the Mark and Mary Stevens Neuroimaging and Informatics Institute (Stevens INI) at the Keck School of Medicine of USC will lead a worldwide effort to map how eight common psychiatric disorders affect brain function, supported by a five-year, $3.2 million grant from the National Institutes of Health.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5071,34 +4201,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261016070646.htm</t>
+          <t xml:space="preserve">https://www.news-medical.net/news/20261021/Global-study-aims-to-map-brain-changes-across-eight-psychiatric-disorders.aspx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-16</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Transmitter</t>
+          <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Highly cited autism paper earns expression of concern over data duplications</t>
+          <t xml:space="preserve">Prenatal iron deficiency linked to lasting changes in the offspring brain</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">The notice, published in Nature last week, also addressed an image duplication identified by a prominent research-integrity sleuth.</t>
+          <t xml:space="preserve">During the first weeks of pregnancy, developing cells are already laying the foundation for the brain. Iron plays a major role in the organization and shaping of cells during this stage of gestation.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5108,34 +4238,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/highly-cited-autism-paper-earns-expression-of-concern-over-data-duplications/</t>
+          <t xml:space="preserve">https://www.news-medical.net/news/20261021/Prenatal-iron-deficiency-linked-to-lasting-changes-in-the-offspring-brain.aspx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ScienceDaily</t>
+          <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rare study reveals a striking divide inside an Alzheimer’s patient’s brain</t>
+          <t xml:space="preserve">Japanese study links postpartum depression to mother-infant bonding difficulties</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A rare examination of an Alzheimer’s patient’s brain revealed that regions cleared of amyloid plaques had remarkably little of the harmful tau buildup associated with memory loss, while neighboring areas showed extensive damage. The discovery suggests that removing amyloid may have lasting protective effects and could help slow Alzheimer’s progression, especially when treatment begins early.</t>
+          <t xml:space="preserve">A Japanese study found that higher postpartum depression scores were associated with greater mother–infant bonding difficulties.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5145,34 +4275,34 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261013015814.htm</t>
+          <t xml:space="preserve">https://www.news-medical.net/news/20261021/Japanese-study-links-postpartum-depression-to-mother-infant-bonding-difficulties.aspx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Transmitter</t>
+          <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acetaminophen effects on developing brain organoids; and more</t>
+          <t xml:space="preserve">Paternal age may influence sex-specific gene expression changes in embryos</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Here is a roundup of autism-related news and research spotted around the web for the week of 12 October.</t>
+          <t xml:space="preserve">When genes are "expressed," it is like reading an instruction manual to create things the body needs - such as proteins or RNA.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5182,54 +4312,202 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/acetaminophen-effects-on-developing-brain-organoids-and-more/</t>
+          <t xml:space="preserve">https://www.news-medical.net/news/20261020/Paternal-age-may-influence-sex-specific-gene-expression-changes-in-embryos.aspx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-13</t>
+          <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t xml:space="preserve">ScienceDaily</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientists find a way to fight Alzheimer’s brain damage without removing toxic tau</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientists have found a promising way to protect the brain from Alzheimer’s-related damage by blocking immune cells that contribute to the destruction of neurons. In mice, the treatment preserved roughly 40% more tissue in memory centers and improved memory, even without removing harmful tau protein buildup.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261019093355.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t xml:space="preserve">The Transmitter</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Private initiative makes ‘historic’ investment in autism research</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aligning Research to Impact Autism has committed more than $450 million to build a new multidisciplinary research network to uncover the roots of profound autism and develop treatments.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/private-initiative-makes-historic-investment-in-autism-research/</t>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">COVID-19 and influenza effects in pregnancy; and more</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Here is a roundup of autism-related news and research spotted around the web for the week of 19 October.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/covid-19-and-influenza-effects-in-pregnancy-and-more/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ScienceDaily</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Why some people escape Alzheimer’s despite carrying a high-risk gene</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientists have discovered why some people with a high genetic risk of Alzheimer’s remain mentally sharp into their 80s, uncovering a rare mutation that protects the brain from harmful protein buildup. The findings reveal a potential new way to prevent early brain damage and could pave the way for treatments that mimic this natural defense.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-20</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261018205044.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ScienceDaily</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Magic mushroom ingredient takes the fight out of aggressive fish</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A psychedelic compound found in magic mushrooms appears to have an unexpected effect: calming highly aggressive fish. Researchers discovered that low doses of psilocybin significantly reduced aggressive attacks in mangrove rivulus fish without disrupting their normal social interactions. The findings suggest psilocybin may selectively calm escalating aggression rather than simply suppressing all behavior.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Small molecule</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261017230036.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-17</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ScienceDaily</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientists find a youth protein that helps aging brain cells act young again</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scientists have discovered that a protein linked to youth helps protect the brain’s immune cells from age-related decline. Restoring the protein in older mice improved the cells’ ability to clear debris and reduced signs of inflammation, raising hopes for future treatments targeting brain aging and Alzheimer’s disease.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-18</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261016070646.htm</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G14"/>
 </worksheet>
 </file>
 
@@ -5352,7 +4630,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -5419,7 +4697,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5434,7 +4712,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -5444,7 +4722,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-08</t>
+          <t xml:space="preserve">2026-10-01</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -5486,7 +4764,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5553,7 +4831,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5568,7 +4846,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5578,7 +4856,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-08</t>
+          <t xml:space="preserve">2026-10-01</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -5620,7 +4898,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5687,7 +4965,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-15</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5728,20 +5006,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L1"/>
   <cols>
-    <col min="1" max="1" width="15"/>
-    <col min="2" max="2" width="12"/>
+    <col min="1" max="1" width="9"/>
+    <col min="2" max="2" width="11"/>
     <col min="3" max="3" width="12"/>
-    <col min="4" max="4" width="70"/>
+    <col min="4" max="4" width="9"/>
     <col min="5" max="5" width="9"/>
     <col min="6" max="6" width="9"/>
     <col min="7" max="7" width="10"/>
     <col min="8" max="8" width="10"/>
     <col min="9" max="9" width="10"/>
     <col min="10" max="10" width="18"/>
-    <col min="11" max="11" width="10"/>
-    <col min="12" max="12" width="43"/>
+    <col min="11" max="11" width="9"/>
+    <col min="12" max="12" width="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5806,131 +5084,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gloria B Choi</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-08</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Editorial Expression of Concern: Maternal gut bacteria promote neurodevelopmental abnormalities in mouse offspring.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nature</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">middle</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10/11</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">other</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">affiliation</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42850426</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42850426/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jun R Huh</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-08</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-15</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Editorial Expression of Concern: Maternal gut bacteria promote neurodevelopmental abnormalities in mouse offspring.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nature</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">senior</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11/11</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">other</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">affiliation</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42850426</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://pubmed.ncbi.nlm.nih.gov/42850426/</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
 </worksheet>
 </file>
--- a/atlas-weekly.xlsx
+++ b/atlas-weekly.xlsx
@@ -252,7 +252,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24T08:58:52</t>
+          <t xml:space="preserve">2026-10-24T09:08:07</t>
         </is>
       </c>
     </row>
@@ -2329,17 +2329,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">0.6</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2503,17 +2503,17 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2.0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2590,17 +2590,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1.5</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">212</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2851,17 +2851,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">10.9</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">83</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3199,17 +3199,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">4.1</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">310</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">

--- a/atlas-weekly.xlsx
+++ b/atlas-weekly.xlsx
@@ -137,7 +137,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18T20:22:12</t>
+          <t xml:space="preserve">2026-10-25T21:15:41</t>
         </is>
       </c>
     </row>
@@ -149,7 +149,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -159,7 +159,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24T08:57:28</t>
+          <t xml:space="preserve">2026-10-25T21:15:14</t>
         </is>
       </c>
     </row>
@@ -228,7 +228,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-17</t>
+          <t xml:space="preserve">2026-10-18</t>
         </is>
       </c>
     </row>
@@ -240,7 +240,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-10-25</t>
         </is>
       </c>
     </row>
@@ -252,7 +252,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24T09:08:07</t>
+          <t xml:space="preserve">2026-10-25T21:16:23</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <cols>
     <col min="1" max="1" width="12"/>
     <col min="2" max="2" width="17"/>
@@ -4469,45 +4469,8 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-17</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ScienceDaily</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scientists find a youth protein that helps aging brain cells act young again</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Scientists have discovered that a protein linked to youth helps protect the brain’s immune cells from age-related decline. Restoring the protein in older mice improved the cells’ ability to clear debris and reduced signs of inflammation, raising hopes for future treatments targeting brain aging and Alzheimer’s disease.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-18</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261016070646.htm</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G13"/>
 </worksheet>
 </file>
 

--- a/atlas-weekly.xlsx
+++ b/atlas-weekly.xlsx
@@ -149,7 +149,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -159,7 +159,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25T21:15:14</t>
+          <t xml:space="preserve">2026-10-26T23:10:01</t>
         </is>
       </c>
     </row>
@@ -228,7 +228,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-18</t>
+          <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
     </row>
@@ -240,7 +240,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25</t>
+          <t xml:space="preserve">2026-10-26</t>
         </is>
       </c>
     </row>
@@ -252,7 +252,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25T21:16:23</t>
+          <t xml:space="preserve">2026-10-26T23:10:12</t>
         </is>
       </c>
     </row>
@@ -2677,17 +2677,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1.3</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3373,17 +3373,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">1.3</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OpenAlex 2-yr citedness</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">59</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3977,13 +3977,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <cols>
     <col min="1" max="1" width="12"/>
     <col min="2" max="2" width="17"/>
     <col min="3" max="3" width="70"/>
     <col min="4" max="4" width="70"/>
-    <col min="5" max="5" width="16"/>
+    <col min="5" max="5" width="12"/>
     <col min="6" max="6" width="12"/>
     <col min="7" max="7" width="70"/>
   </cols>
@@ -4432,45 +4432,8 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-18</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ScienceDaily</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Magic mushroom ingredient takes the fight out of aggressive fish</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A psychedelic compound found in magic mushrooms appears to have an unexpected effect: calming highly aggressive fish. Researchers discovered that low doses of psilocybin significantly reduced aggressive attacks in mangrove rivulus fish without disrupting their normal social interactions. The findings suggest psilocybin may selectively calm escalating aggression rather than simply suppressing all behavior.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Small molecule</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-18</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261017230036.htm</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G13"/>
+  <autoFilter ref="A1:G12"/>
 </worksheet>
 </file>
 

--- a/atlas-weekly.xlsx
+++ b/atlas-weekly.xlsx
@@ -149,7 +149,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -159,7 +159,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-26T23:10:01</t>
+          <t xml:space="preserve">2026-10-28T02:20:55</t>
         </is>
       </c>
     </row>
@@ -228,7 +228,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
     </row>
@@ -240,7 +240,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-26</t>
+          <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
     </row>
@@ -252,7 +252,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-26T23:10:12</t>
+          <t xml:space="preserve">2026-10-28T02:21:04</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <cols>
     <col min="1" max="1" width="12"/>
     <col min="2" max="2" width="17"/>
@@ -4028,7 +4028,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-23</t>
+          <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientists discover a hidden messaging system deep inside the brain</t>
+          <t xml:space="preserve">The autistic brain processes faces differently than scientists thought</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">A tiny region deep within the brain has surprised scientists by revealing a remarkably sophisticated communication system. Previously thought to broadcast the same chemical signal throughout the brain, this region actually sends targeted messages that help control learning, attention, and behavior, according to new research in mice.</t>
+          <t xml:space="preserve">A major new study reveals that autistic children’s brains process faces differently, and those differences may begin earlier than scientists previously thought. Researchers found that brain signals associated with recognizing faces become more specialized as neurotypical children grow older, but show much less change in autistic children. The discovery could help explain why some autistic people have difficulty recognizing faces and reading emotions.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4053,34 +4053,34 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261022081304.htm</t>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261027063824.htm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-22</t>
+          <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ScienceDaily</t>
+          <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientists discover a surprising secret behind the human brain’s wrinkles</t>
+          <t xml:space="preserve">Autistic people report worse menopause symptoms and lower quality of life</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientists have discovered why common marmosets have unusually small, smooth brains despite starting development much like other primates. The secret lies in subtle changes to brain-building cells that slow neuron production, revealing new clues about how the large, folded human brain evolved.</t>
+          <t xml:space="preserve">A new study by researchers at Bournemouth University has shown that autistic people consistently experience more severe menopausal symptoms than non-autistic people, leading to poorer wellbeing and quality of life.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4090,19 +4090,19 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261021231235.htm</t>
+          <t xml:space="preserve">https://www.news-medical.net/news/20261027/Autistic-people-report-worse-menopause-symptoms-and-lower-quality-of-life.aspx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-22</t>
+          <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Depression profile linked to disrupted sleep and poorer treatment responses</t>
+          <t xml:space="preserve">Rutgers study links prenatal wildfire smoke exposure to autism risk</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This study uncovers a circadian depression subtype, revealing links between sleep patterns, symptom severity, and antidepressant response in a large cohort.</t>
+          <t xml:space="preserve">A Rutgers-led analysis of health insurance records found that exposure to fine particles from wildfire smoke during pregnancy was associated with a higher risk of autism diagnosis in children, with the strongest associations during the second and third trimesters.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4127,34 +4127,34 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.news-medical.net/news/20261022/Depression-profile-linked-to-disrupted-sleep-and-poorer-treatment-responses.aspx</t>
+          <t xml:space="preserve">https://www.news-medical.net/news/20261027/Rutgers-study-links-prenatal-wildfire-smoke-exposure-to-autism-risk.aspx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-22</t>
+          <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Transmitter</t>
+          <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevalence of profound autism declines with new definition</t>
+          <t xml:space="preserve">Early exercise improves motor function in a mouse model of DDX3X syndrome</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">The updated, more precise definition used in a CDC study includes adaptive scores.</t>
+          <t xml:space="preserve">Acquisition of motor skills during infancy is critical for a child's ability to interact with the physical and social environment and motor impairments are frequent in individuals with neurodevelopmental disorders, including autism.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4164,19 +4164,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/prevalence-of-profound-autism-declines-with-new-definition/</t>
+          <t xml:space="preserve">https://www.news-medical.net/news/20261027/Early-exercise-improves-motor-function-in-a-mouse-model-of-DDX3X-syndrome.aspx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Global study aims to map brain changes across eight psychiatric disorders</t>
+          <t xml:space="preserve">Autistic people show weaker brain responses to negative feedback</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Researchers from the Mark and Mary Stevens Neuroimaging and Informatics Institute (Stevens INI) at the Keck School of Medicine of USC will lead a worldwide effort to map how eight common psychiatric disorders affect brain function, supported by a five-year, $3.2 million grant from the National Institutes of Health.</t>
+          <t xml:space="preserve">Some people who have autism spectrum disorder struggle to adapt to changing demands in their environment.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4201,34 +4201,34 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.news-medical.net/news/20261021/Global-study-aims-to-map-brain-changes-across-eight-psychiatric-disorders.aspx</t>
+          <t xml:space="preserve">https://www.news-medical.net/news/20261027/Autistic-people-show-weaker-brain-responses-to-negative-feedback.aspx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">News-Medical</t>
+          <t xml:space="preserve">The Transmitter</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prenatal iron deficiency linked to lasting changes in the offspring brain</t>
+          <t xml:space="preserve">Behavioral phenomics in zebrafish; and more</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">During the first weeks of pregnancy, developing cells are already laying the foundation for the brain. Iron plays a major role in the organization and shaping of cells during this stage of gestation.</t>
+          <t xml:space="preserve">Here is a roundup of autism-related news and research spotted around the web for the week of 26 October.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4238,34 +4238,34 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-10-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.news-medical.net/news/20261021/Prenatal-iron-deficiency-linked-to-lasting-changes-in-the-offspring-brain.aspx</t>
+          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/behavioral-phenomics-in-zebrafish-and-more/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-21</t>
+          <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">News-Medical</t>
+          <t xml:space="preserve">ScienceDaily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japanese study links postpartum depression to mother-infant bonding difficulties</t>
+          <t xml:space="preserve">Scientists discover a hidden messaging system deep inside the brain</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Japanese study found that higher postpartum depression scores were associated with greater mother–infant bonding difficulties.</t>
+          <t xml:space="preserve">A tiny region deep within the brain has surprised scientists by revealing a remarkably sophisticated communication system. Previously thought to broadcast the same chemical signal throughout the brain, this region actually sends targeted messages that help control learning, attention, and behavior, according to new research in mice.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4280,29 +4280,29 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.news-medical.net/news/20261021/Japanese-study-links-postpartum-depression-to-mother-infant-bonding-difficulties.aspx</t>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261022081304.htm</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">News-Medical</t>
+          <t xml:space="preserve">ScienceDaily</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paternal age may influence sex-specific gene expression changes in embryos</t>
+          <t xml:space="preserve">Scientists discover a surprising secret behind the human brain’s wrinkles</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">When genes are "expressed," it is like reading an instruction manual to create things the body needs - such as proteins or RNA.</t>
+          <t xml:space="preserve">Scientists have discovered why common marmosets have unusually small, smooth brains despite starting development much like other primates. The secret lies in subtle changes to brain-building cells that slow neuron production, revealing new clues about how the large, folded human brain evolved.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4317,29 +4317,29 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.news-medical.net/news/20261020/Paternal-age-may-influence-sex-specific-gene-expression-changes-in-embryos.aspx</t>
+          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261021231235.htm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ScienceDaily</t>
+          <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientists find a way to fight Alzheimer’s brain damage without removing toxic tau</t>
+          <t xml:space="preserve">Depression profile linked to disrupted sleep and poorer treatment responses</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientists have found a promising way to protect the brain from Alzheimer’s-related damage by blocking immune cells that contribute to the destruction of neurons. In mice, the treatment preserved roughly 40% more tissue in memory centers and improved memory, even without removing harmful tau protein buildup.</t>
+          <t xml:space="preserve">This study uncovers a circadian depression subtype, revealing links between sleep patterns, symptom severity, and antidepressant response in a large cohort.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4349,19 +4349,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261019093355.htm</t>
+          <t xml:space="preserve">https://www.news-medical.net/news/20261022/Depression-profile-linked-to-disrupted-sleep-and-poorer-treatment-responses.aspx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COVID-19 and influenza effects in pregnancy; and more</t>
+          <t xml:space="preserve">Prevalence of profound autism declines with new definition</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Here is a roundup of autism-related news and research spotted around the web for the week of 19 October.</t>
+          <t xml:space="preserve">The updated, more precise definition used in a CDC study includes adaptive scores.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4386,34 +4386,34 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/covid-19-and-influenza-effects-in-pregnancy-and-more/</t>
+          <t xml:space="preserve">https://www.thetransmitter.org/spectrum/prevalence-of-profound-autism-declines-with-new-definition/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-19</t>
+          <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">ScienceDaily</t>
+          <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Why some people escape Alzheimer’s despite carrying a high-risk gene</t>
+          <t xml:space="preserve">Global study aims to map brain changes across eight psychiatric disorders</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scientists have discovered why some people with a high genetic risk of Alzheimer’s remain mentally sharp into their 80s, uncovering a rare mutation that protects the brain from harmful protein buildup. The findings reveal a potential new way to prevent early brain damage and could pave the way for treatments that mimic this natural defense.</t>
+          <t xml:space="preserve">Researchers from the Mark and Mary Stevens Neuroimaging and Informatics Institute (Stevens INI) at the Keck School of Medicine of USC will lead a worldwide effort to map how eight common psychiatric disorders affect brain function, supported by a five-year, $3.2 million grant from the National Institutes of Health.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4423,17 +4423,91 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-20</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.sciencedaily.com/releases/2026/10/261018205044.htm</t>
+          <t xml:space="preserve">https://www.news-medical.net/news/20261021/Global-study-aims-to-map-brain-changes-across-eight-psychiatric-disorders.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">News-Medical</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prenatal iron deficiency linked to lasting changes in the offspring brain</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">During the first weeks of pregnancy, developing cells are already laying the foundation for the brain. Iron plays a major role in the organization and shaping of cells during this stage of gestation.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-24</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.news-medical.net/news/20261021/Prenatal-iron-deficiency-linked-to-lasting-changes-in-the-offspring-brain.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">News-Medical</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Japanese study links postpartum depression to mother-infant bonding difficulties</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Japanese study found that higher postpartum depression scores were associated with greater mother–infant bonding difficulties.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-24</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.news-medical.net/news/20261021/Japanese-study-links-postpartum-depression-to-mother-infant-bonding-difficulties.aspx</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G14"/>
 </worksheet>
 </file>
 

--- a/atlas-weekly.xlsx
+++ b/atlas-weekly.xlsx
@@ -89,7 +89,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J97"/>
   <cols>
     <col min="1" max="1" width="60"/>
     <col min="2" max="2" width="60"/>
@@ -113,7 +113,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Window: 2026-10-21 to 2026-10-28 (last 7 days) · generated 2026-10-28T11:06 · library refreshed 2026-10-24</t>
+          <t xml:space="preserve">Window: 2026-10-21 to 2026-10-28 (last 7 days) · generated 2026-10-28T11:12 · library refreshed 2026-10-24</t>
         </is>
       </c>
     </row>
@@ -141,877 +141,862 @@
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Window used</t>
+          <t xml:space="preserve">Windows compared</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Publications added or published</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">−10</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">last 7 days (2026-10-21 to 2026-10-28)</t>
+          <t xml:space="preserve">Each lane counts the rows dated inside its own window, ending today; the previous window is the same number of days immediately before it, counted by the same rule; Change is this minus previous.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Press releases</t>
+          <t xml:space="preserve">Publications added or published</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">+5</t>
+          <t xml:space="preserve">−10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">last 7 days (2026-10-21 to 2026-10-28)</t>
+          <t xml:space="preserve">last 7 days (2026-10-21 to 2026-10-28), previous 2026-10-13 to 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">NIH awards noticed</t>
+          <t xml:space="preserve">Press releases</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">503</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">−69</t>
+          <t xml:space="preserve">+3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">last 90 days (2026-07-30 to 2026-10-28)</t>
+          <t xml:space="preserve">last 7 days (2026-10-21 to 2026-10-28), previous 2026-10-13 to 2026-10-20</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">NIH dollars noticed</t>
+          <t xml:space="preserve">NIH awards noticed</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">$259.2M</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">$274.7M</t>
+          <t xml:space="preserve">505</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">−$15.5M</t>
+          <t xml:space="preserve">−71</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">last 90 days (2026-07-30 to 2026-10-28)</t>
+          <t xml:space="preserve">last 90 days (2026-07-30 to 2026-10-28), previous 2026-04-30 to 2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinical trials updated (12 new)</t>
+          <t xml:space="preserve">NIH dollars noticed</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve">$259.2M</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve">$275.7M</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">−$16.5M</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">last 30 days (2026-09-28 to 2026-10-28)</t>
+          <t xml:space="preserve">last 90 days (2026-07-30 to 2026-10-28), previous 2026-04-30 to 2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patents published or granted</t>
+          <t xml:space="preserve">Clinical trials updated (12 new)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">75</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">78</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">−7</t>
+          <t xml:space="preserve">−3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">last 90 days (2026-07-30 to 2026-10-28)</t>
+          <t xml:space="preserve">last 30 days (2026-09-28 to 2026-10-28), previous 2026-08-28 to 2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t xml:space="preserve">Patents published or granted</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">−8</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">last 90 days (2026-07-30 to 2026-10-28), previous 2026-04-30 to 2026-07-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tracked-author papers</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">nothing in the last 7 days — the 25 most recent instead</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">HIGHLIGHTS</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t xml:space="preserve">Top 10 of 40 papers in this window, ranked by journal impact × priority × therapeutic modality × citations</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">#</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Published</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Title</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">First author</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Journal</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">IF</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Priority</t>
         </is>
       </c>
-      <c r="H14" s="1" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Modalities</t>
         </is>
       </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="I15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Why it surfaced</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr">
+      <c r="J15" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">PMID</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
-      <c r="C15" s="3" t="str">
+      <c r="C16" s="3" t="str">
         <f>HYPERLINK("https://pubmed.ncbi.nlm.nih.gov/42914007/","Cariprazine in the Treatment of Pediatric Patients With Irritability Associated With Autism Spectrum Disorder: A Randomized Controlled Trial.")</f>
         <v>Cariprazine in the Treatment of Pediatric Patients With Irritability Associated With Autism Spectrum Disorder: A Randomized Controlled Trial.</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">Findling RL</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t xml:space="preserve">Journal of the American Academy of Child &amp; Adolescent Psychiatry</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t xml:space="preserve">9.2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t xml:space="preserve">Clinical trial</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t xml:space="preserve">Journal of the American Academy of Child &amp; Adolescent Psychiatry (IF 9.2) · Clinical trial</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t xml:space="preserve">42914007</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
-      <c r="C16" s="3" t="str">
+      <c r="C17" s="3" t="str">
         <f>HYPERLINK("https://pubmed.ncbi.nlm.nih.gov/42881222/","Spatiotemporal AI-based modeling of gene regulation and variant effects in the developing human brain using Seal.")</f>
         <v>Spatiotemporal AI-based modeling of gene regulation and variant effects in the developing human brain using Seal.</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t xml:space="preserve">Hao Y</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nature Neuroscience</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t xml:space="preserve">21.2</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t xml:space="preserve">Clinical observation</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t xml:space="preserve">Nature Neuroscience (IF 21.2) · Clinical observation · 1 citation</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t xml:space="preserve">42881222</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t xml:space="preserve">3</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
-      <c r="C17" s="3" t="str">
+      <c r="C18" s="3" t="str">
         <f>HYPERLINK("https://pubmed.ncbi.nlm.nih.gov/42911480/","Feasibility, Acceptability, and Efficacy of an Ecological Momentary Intervention for Autistic Adults.")</f>
         <v>Feasibility, Acceptability, and Efficacy of an Ecological Momentary Intervention for Autistic Adults.</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t xml:space="preserve">Parenteau CI</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t xml:space="preserve">3.2</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t xml:space="preserve">Clinical trial</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t xml:space="preserve">Journal of Autism and Developmental Disorders (IF 3.2) · Clinical trial</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t xml:space="preserve">42911480</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
-      <c r="C18" s="3" t="str">
+      <c r="C19" s="3" t="str">
         <f>HYPERLINK("https://pubmed.ncbi.nlm.nih.gov/42911477/","Fatty Acid Supplementation in Toddlers Born Preterm and Attention and Autism Outcomes at 8-10 Years: Omega Tots Randomized Controlled Trial Long-Term Follow-Up.")</f>
         <v>Fatty Acid Supplementation in Toddlers Born Preterm and Attention and Autism Outcomes at 8-10 Years: Omega Tots Randomized Controlled Trial Long-Term Follow-Up.</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">Robinette LM</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t xml:space="preserve">Journal of Autism and Developmental Disorders</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t xml:space="preserve">3.2</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t xml:space="preserve">Clinical trial</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t xml:space="preserve">Journal of Autism and Developmental Disorders (IF 3.2) · Clinical trial</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t xml:space="preserve">42911477</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
-      <c r="C19" s="3" t="str">
+      <c r="C20" s="3" t="str">
         <f>HYPERLINK("https://pubmed.ncbi.nlm.nih.gov/42901987/","The landscape of gene loss and missense variation across the mammalian tree informs on gene essentiality.")</f>
         <v>The landscape of gene loss and missense variation across the mammalian tree informs on gene essentiality.</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t xml:space="preserve">Liao C</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nature Genetics</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t xml:space="preserve">29.0</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t xml:space="preserve">Unclassified</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t xml:space="preserve">Nature Genetics (IF 29.0)</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t xml:space="preserve">42901987</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-17</t>
         </is>
       </c>
-      <c r="C20" s="3" t="str">
+      <c r="C21" s="3" t="str">
         <f>HYPERLINK("https://pubmed.ncbi.nlm.nih.gov/42892634/","A microglial basis for fragile X syndrome via impairment of FMRP-regulated lysosomal function.")</f>
         <v>A microglial basis for fragile X syndrome via impairment of FMRP-regulated lysosomal function.</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t xml:space="preserve">Li H</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t xml:space="preserve">Molecular Psychiatry</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t xml:space="preserve">11.0</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t xml:space="preserve">Mechanistic / basic</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t xml:space="preserve">Molecular Psychiatry (IF 11.0) · Mechanistic / basic · 1 citation</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t xml:space="preserve">42892634</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">7</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
-      <c r="C21" s="3" t="str">
+      <c r="C22" s="3" t="str">
         <f>HYPERLINK("https://pubmed.ncbi.nlm.nih.gov/42905887/","KATNAL2 dysfunction impairs microtubule dynamics and contributes to syndromic neurodevelopmental disease.")</f>
         <v>KATNAL2 dysfunction impairs microtubule dynamics and contributes to syndromic neurodevelopmental disease.</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t xml:space="preserve">Sönmezler E</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t xml:space="preserve">Human molecular genetics</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">3.2</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t xml:space="preserve">Bench-to-bedside</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t xml:space="preserve">Human molecular genetics (IF 3.2) · Bench-to-bedside</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t xml:space="preserve">42905887</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
-      <c r="C22" s="3" t="str">
+      <c r="C23" s="3" t="str">
         <f>HYPERLINK("https://pubmed.ncbi.nlm.nih.gov/42919820/","Psychological and Neurodevelopmental Correlates of Extreme Demand Avoidance in a Clinical Sample, an Exploratory Study.")</f>
         <v>Psychological and Neurodevelopmental Correlates of Extreme Demand Avoidance in a Clinical Sample, an Exploratory Study.</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t xml:space="preserve">Lack O</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t xml:space="preserve">Autism Research</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">5.2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t xml:space="preserve">Clinical observation</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t xml:space="preserve">Autism Research (IF 5.2) · Clinical observation</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t xml:space="preserve">42919820</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-15</t>
         </is>
       </c>
-      <c r="C23" s="3" t="str">
+      <c r="C24" s="3" t="str">
         <f>HYPERLINK("https://pubmed.ncbi.nlm.nih.gov/42892189/","Predicting individual differences in social functioning from functional connectomes in children with autism spectrum disorder.")</f>
         <v>Predicting individual differences in social functioning from functional connectomes in children with autism spectrum disorder.</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">Li A</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t xml:space="preserve">Psychiatry research</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">4.6</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t xml:space="preserve">Clinical observation</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t xml:space="preserve">Psychiatry research (IF 4.6) · Clinical observation</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t xml:space="preserve">42892189</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t xml:space="preserve">10</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
-      <c r="C24" s="3" t="str">
+      <c r="C25" s="3" t="str">
         <f>HYPERLINK("https://pubmed.ncbi.nlm.nih.gov/42911835/","Multimodal Analysis of Brain Network Abnormalities in Autism Spectrum Disorder: a Graph Neural Network-based Fusion Investigation of EEG and fNIRS.")</f>
         <v>Multimodal Analysis of Brain Network Abnormalities in Autism Spectrum Disorder: a Graph Neural Network-based Fusion Investigation of EEG and fNIRS.</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t xml:space="preserve">Li Y</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t xml:space="preserve">IEEE transactions on bio-medical engineering</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">4.1</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t xml:space="preserve">Clinical observation</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t xml:space="preserve">IEEE transactions on bio-medical engineering (IF 4.1) · Clinical observation</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t xml:space="preserve">42911835</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BY BRANCH</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">This window</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Previous window</t>
-        </is>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Previous (2026-10-13 to 2026-10-20)</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Change</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Behavioral &amp; Developmental</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">+2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Intervention &amp; Clinical</t>
+          <t xml:space="preserve">Behavioral &amp; Developmental</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">−5</t>
+          <t xml:space="preserve">+2</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Genetics &amp; Molecular</t>
+          <t xml:space="preserve">Intervention &amp; Clinical</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">−1</t>
+          <t xml:space="preserve">−5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
+          <t xml:space="preserve">Genetics &amp; Molecular</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1023,96 +1008,96 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cytokines &amp; Inflammation</t>
+          <t xml:space="preserve">Neuroscience &amp; Imaging</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">−4</t>
+          <t xml:space="preserve">−1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t xml:space="preserve">Cytokines &amp; Inflammation</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">−4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t xml:space="preserve">Neuroimmunology</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t xml:space="preserve">1</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t xml:space="preserve">2</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t xml:space="preserve">−1</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BY THERAPEUTIC MODALITY</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="B35" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">This window</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Previous window</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Previous (2026-10-13 to 2026-10-20)</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Change</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gene therapy</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">−1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nucleic acid therapeutics</t>
+          <t xml:space="preserve">Gene therapy</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1122,19 +1107,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">−1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viral vector</t>
+          <t xml:space="preserve">Nucleic acid therapeutics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1156,7 +1141,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antibody</t>
+          <t xml:space="preserve">Viral vector</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1178,7 +1163,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Peptide</t>
+          <t xml:space="preserve">Antibody</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1200,7 +1185,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Small molecule</t>
+          <t xml:space="preserve">Peptide</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1210,19 +1195,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">−1</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Device / stimulation</t>
+          <t xml:space="preserve">Small molecule</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1244,1208 +1229,1230 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t xml:space="preserve">Device / stimulation</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">−1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t xml:space="preserve">Behavioral</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t xml:space="preserve">0</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t xml:space="preserve">5</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t xml:space="preserve">−5</t>
         </is>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">NIH GRANTS</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t xml:space="preserve">434 awards noticed, $259.2M — last 90 days (2026-07-30 to 2026-10-28)</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Notice</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
+      <c r="B46" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Project</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Title</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="D46" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Contact PI</t>
         </is>
       </c>
-      <c r="E45" s="1" t="inlineStr">
+      <c r="E46" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Organization</t>
         </is>
       </c>
-      <c r="F45" s="1" t="inlineStr">
+      <c r="F46" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Award</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+    <row r="47">
+      <c r="A47" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-27</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t xml:space="preserve">5U2CHL156291-07</t>
         </is>
       </c>
-      <c r="C46" s="3" t="str">
+      <c r="C47" s="3" t="str">
         <f>HYPERLINK("https://reporter.nih.gov/project-details/11525080","The INCLUDE Data Coordinating Center")</f>
         <v>The INCLUDE Data Coordinating Center</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t xml:space="preserve">Adam Cain Resnick</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t xml:space="preserve">CHILDREN'S HOSP OF PHILADELPHIA</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t xml:space="preserve">$6.0M</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-14</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t xml:space="preserve">5U24AG092191-03</t>
         </is>
       </c>
-      <c r="C47" s="3" t="str">
+      <c r="C48" s="3" t="str">
         <f>HYPERLINK("https://reporter.nih.gov/project-details/11385482","The INCLUDE Project Down Syndrome Biorepository (DS-Biorepository)")</f>
         <v>The INCLUDE Project Down Syndrome Biorepository (DS-Biorepository)</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t xml:space="preserve">Joaquin M. Espinosa</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIVERSITY OF COLORADO DENVER</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t xml:space="preserve">$5.3M</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-14</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t xml:space="preserve">5UM1MH130991-05</t>
         </is>
       </c>
-      <c r="C48" s="3" t="str">
+      <c r="C49" s="3" t="str">
         <f>HYPERLINK("https://reporter.nih.gov/project-details/11417222","A Multidisciplinary Center for Developing Human and Non-human Primate Brain Cell Atlases")</f>
         <v>A Multidisciplinary Center for Developing Human and Non-human Primate Brain Cell Atlases</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t xml:space="preserve">ARNOLD KRIEGSTEIN</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t xml:space="preserve">UNIVERSITY OF CALIFORNIA, SAN FRANCISCO</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t xml:space="preserve">$4.7M</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-21</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t xml:space="preserve">5U19NS132720-04</t>
         </is>
       </c>
-      <c r="C49" s="3" t="str">
+      <c r="C50" s="3" t="str">
         <f>HYPERLINK("https://reporter.nih.gov/project-details/11385500","Mechanisms of neural circuit dynamics in working memory and decision-making")</f>
         <v>Mechanisms of neural circuit dynamics in working memory and decision-making</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t xml:space="preserve">Carlos D Brody</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t xml:space="preserve">PRINCETON UNIVERSITY</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t xml:space="preserve">$4.2M</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-08-04</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t xml:space="preserve">5U19NS107616-09</t>
         </is>
       </c>
-      <c r="C50" s="3" t="str">
+      <c r="C51" s="3" t="str">
         <f>HYPERLINK("https://reporter.nih.gov/project-details/11416774","Oxytocin Modulation of Neural Circuit Function and Behavior")</f>
         <v>Oxytocin Modulation of Neural Circuit Function and Behavior</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t xml:space="preserve">RICHARD W TSIEN</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t xml:space="preserve">NEW YORK UNIVERSITY SCHOOL OF MEDICINE</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t xml:space="preserve">$4.2M</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CLINICAL TRIALS</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t xml:space="preserve">12 new starts, 63 updated — last 30 days (2026-09-28 to 2026-10-28)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Updated</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
+      <c r="B54" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Change</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">NCT number</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr">
+      <c r="D54" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Title</t>
         </is>
       </c>
-      <c r="E53" s="1" t="inlineStr">
+      <c r="E54" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="F53" s="1" t="inlineStr">
+      <c r="F54" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sponsor</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-21</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t xml:space="preserve">new study</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t xml:space="preserve">NCT07887243</t>
         </is>
       </c>
-      <c r="D54" s="3" t="str">
+      <c r="D55" s="3" t="str">
         <f>HYPERLINK("https://clinicaltrials.gov/study/NCT07887243","Adapting the Sensory Environment to Reduce Stress in Children With Autism During Dental Visits")</f>
         <v>Adapting the Sensory Environment to Reduce Stress in Children With Autism During Dental Visits</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t xml:space="preserve">active not recruiting</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t xml:space="preserve">Jagiellonian University</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-20</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t xml:space="preserve">new study</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t xml:space="preserve">NCT07884032</t>
         </is>
       </c>
-      <c r="D55" s="3" t="str">
+      <c r="D56" s="3" t="str">
         <f>HYPERLINK("https://clinicaltrials.gov/study/NCT07884032","Expression Intensity Modulates Social Intention Understanding in ASD Children")</f>
         <v>Expression Intensity Modulates Social Intention Understanding in ASD Children</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t xml:space="preserve">not yet recruiting</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t xml:space="preserve">University of Electronic Science and Technology of China</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-19</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t xml:space="preserve">new study</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t xml:space="preserve">NCT07880028</t>
         </is>
       </c>
-      <c r="D56" s="3" t="str">
+      <c r="D57" s="3" t="str">
         <f>HYPERLINK("https://clinicaltrials.gov/study/NCT07880028","Adapted Group Therapy Compared With Usual Care for Anxiety and Depression in Adults With an Autism Diagnosis")</f>
         <v>Adapted Group Therapy Compared With Usual Care for Anxiety and Depression in Adults With an Autism Diagnosis</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t xml:space="preserve">not yet recruiting</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t xml:space="preserve">Lovisenberg Diakonale Hospital</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-16</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t xml:space="preserve">new study</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t xml:space="preserve">NCT07812233</t>
         </is>
       </c>
-      <c r="D57" s="3" t="str">
+      <c r="D58" s="3" t="str">
         <f>HYPERLINK("https://clinicaltrials.gov/study/NCT07812233","Heart Rate Variability Biofeedback for Anxiety in Autistic Youth")</f>
         <v>Heart Rate Variability Biofeedback for Anxiety in Autistic Youth</v>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t xml:space="preserve">recruiting</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t xml:space="preserve">Massachusetts General Hospital</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-09</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t xml:space="preserve">new study</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t xml:space="preserve">NCT07439510</t>
         </is>
       </c>
-      <c r="D58" s="3" t="str">
+      <c r="D59" s="3" t="str">
         <f>HYPERLINK("https://clinicaltrials.gov/study/NCT07439510","A Study to Investigate the Effects and Safety of Codabakalner for the Treatment of FXS in Male Participants and Adult Participants With ADS")</f>
         <v>A Study to Investigate the Effects and Safety of Codabakalner for the Treatment of FXS in Male Participants and Adult Participants With ADS</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t xml:space="preserve">not yet recruiting</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t xml:space="preserve">Spinogenix</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-06</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t xml:space="preserve">new study</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t xml:space="preserve">NCT07859696</t>
         </is>
       </c>
-      <c r="D59" s="3" t="str">
+      <c r="D60" s="3" t="str">
         <f>HYPERLINK("https://clinicaltrials.gov/study/NCT07859696","Effectiveness of Interactive Techniques on Oral Hygiene Skills in a Group of Autistic Egyptian Children")</f>
         <v>Effectiveness of Interactive Techniques on Oral Hygiene Skills in a Group of Autistic Egyptian Children</v>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t xml:space="preserve">not yet recruiting</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t xml:space="preserve">Faculty of Dental Medicine for Girls</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t xml:space="preserve">new study</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t xml:space="preserve">NCT07859345</t>
         </is>
       </c>
-      <c r="D60" s="3" t="str">
+      <c r="D61" s="3" t="str">
         <f>HYPERLINK("https://clinicaltrials.gov/study/NCT07859345","Effects of Virtual Reality-Based Interventions on Fine Motor and Activities of Daily Living Skills in Children Aged 5-10 Years With Autism Spectrum Disorder")</f>
         <v>Effects of Virtual Reality-Based Interventions on Fine Motor and Activities of Daily Living Skills in Children Aged 5-10 Years With Autism Spectrum Disorder</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t xml:space="preserve">not yet recruiting</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t xml:space="preserve">Beyza Asli Bilsel</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-05</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t xml:space="preserve">new study</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t xml:space="preserve">NCT07858617</t>
         </is>
       </c>
-      <c r="D61" s="3" t="str">
+      <c r="D62" s="3" t="str">
         <f>HYPERLINK("https://clinicaltrials.gov/study/NCT07858617","Relation Between Autistic Features and Fine Motor Abilities in Children With Autism Spectrum Disorder")</f>
         <v>Relation Between Autistic Features and Fine Motor Abilities in Children With Autism Spectrum Disorder</v>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t xml:space="preserve">not yet recruiting</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t xml:space="preserve">Cairo University</t>
         </is>
       </c>
     </row>
-    <row r="62"/>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PATENTS</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t xml:space="preserve">8 published or granted — last 90 days (2026-07-30 to 2026-10-28)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Date</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
+      <c r="B65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Title</t>
         </is>
       </c>
-      <c r="D64" s="1" t="inlineStr">
+      <c r="D65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Inventors</t>
         </is>
       </c>
-      <c r="E64" s="1" t="inlineStr">
+      <c r="E65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Assignees</t>
         </is>
       </c>
-      <c r="F64" s="1" t="inlineStr">
+      <c r="F65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">State</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t xml:space="preserve">Published application</t>
         </is>
       </c>
-      <c r="C65" s="3" t="str">
+      <c r="C66" s="3" t="str">
         <f>HYPERLINK("https://patents.google.com/patent/US20260325488A1","METHODS AND COMPOSITIONS FOR TREATING AUTISM USING S-ETHOSUXIMIDE")</f>
         <v>METHODS AND COMPOSITIONS FOR TREATING AUTISM USING S-ETHOSUXIMIDE</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t xml:space="preserve">Charles E. Niesen</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t xml:space="preserve">CA</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-13</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t xml:space="preserve">Granted</t>
         </is>
       </c>
-      <c r="C66" s="3" t="str">
+      <c r="C67" s="3" t="str">
         <f>HYPERLINK("https://patents.google.com/patent/US12758529","USE OF EDARAVONE IN TREATMENT OF AUTISM SPECTRUM DISORDER")</f>
         <v>USE OF EDARAVONE IN TREATMENT OF AUTISM SPECTRUM DISORDER</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t xml:space="preserve">Yi ZHOU; Xin YE</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t xml:space="preserve">SUZHOU AUZONE BIOLOGICAL TECHNOLOGY CO., LTD; SHANGHAI AUZONE BIOLOGICAL TECHNOLOGY CO., LTD.</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t xml:space="preserve">MN</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-22</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t xml:space="preserve">Granted</t>
         </is>
       </c>
-      <c r="C67" s="3" t="str">
+      <c r="C68" s="3" t="str">
         <f>HYPERLINK("https://patents.google.com/patent/US12740725","METHOD AND APPARATUS FOR DETECTING STEREOTYPED BEHAVIOR TO SUPPORT DIAGNOSIS OF AUTISM SPECTRUM DISORDER")</f>
         <v>METHOD AND APPARATUS FOR DETECTING STEREOTYPED BEHAVIOR TO SUPPORT DIAGNOSIS OF AUTISM SPECTRUM DISORDER</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t xml:space="preserve">Cheol-Hwan YOO; Moon-Ki BACK; Jang-Hee YOO; Byung-Ok HAN</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t xml:space="preserve">ELECTRONICS AND TELECOMMUNICATIONS RESEARCH INSTITUTE</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t xml:space="preserve">VA</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t xml:space="preserve">Published application</t>
         </is>
       </c>
-      <c r="C68" s="3" t="str">
+      <c r="C69" s="3" t="str">
         <f>HYPERLINK("https://patents.google.com/patent/US20260269050A1","METHODS AND APPARATUS FOR PREDICTING AND PREVENTING AUTISTIC BEHAVIORS WITH LEARNING AND AI ALGORITHMS")</f>
         <v>METHODS AND APPARATUS FOR PREDICTING AND PREVENTING AUTISTIC BEHAVIORS WITH LEARNING AND AI ALGORITHMS</v>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t xml:space="preserve">Isabelle Mordecai Troxler; Robert Ernest Troxler</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t xml:space="preserve">NC</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-09-03</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t xml:space="preserve">Published application</t>
         </is>
       </c>
-      <c r="C69" s="3" t="str">
+      <c r="C70" s="3" t="str">
         <f>HYPERLINK("https://patents.google.com/patent/US20260256834A1","Materials and Methods for Reducing the Occurrence and/or Severity of Autism Spectrum Disorder")</f>
         <v>Materials and Methods for Reducing the Occurrence and/or Severity of Autism Spectrum Disorder</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t xml:space="preserve">KEN ALIBEK; ANDREW R. LEFKOWITZ</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t xml:space="preserve">FLAASK, LLC</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t xml:space="preserve">VA</t>
         </is>
       </c>
     </row>
-    <row r="70"/>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">PRESS &amp; MEDIA</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t xml:space="preserve">13 releases — last 7 days (2026-10-21 to 2026-10-28)</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="1" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Date</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
+      <c r="B73" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Source</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
+      <c r="C73" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Headline</t>
         </is>
       </c>
-      <c r="D72" s="1" t="inlineStr">
+      <c r="D73" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Modalities</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t xml:space="preserve">ScienceDaily</t>
         </is>
       </c>
-      <c r="C73" s="3" t="str">
+      <c r="C74" s="3" t="str">
         <f>HYPERLINK("https://www.sciencedaily.com/releases/2026/10/261027063824.htm","The autistic brain processes faces differently than scientists thought")</f>
         <v>The autistic brain processes faces differently than scientists thought</v>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
-      <c r="C74" s="3" t="str">
+      <c r="C75" s="3" t="str">
         <f>HYPERLINK("https://www.news-medical.net/news/20261027/Autistic-people-report-worse-menopause-symptoms-and-lower-quality-of-life.aspx","Autistic people report worse menopause symptoms and lower quality of life")</f>
         <v>Autistic people report worse menopause symptoms and lower quality of life</v>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
-      <c r="C75" s="3" t="str">
+      <c r="C76" s="3" t="str">
         <f>HYPERLINK("https://www.news-medical.net/news/20261027/Rutgers-study-links-prenatal-wildfire-smoke-exposure-to-autism-risk.aspx","Rutgers study links prenatal wildfire smoke exposure to autism risk")</f>
         <v>Rutgers study links prenatal wildfire smoke exposure to autism risk</v>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
-      <c r="C76" s="3" t="str">
+      <c r="C77" s="3" t="str">
         <f>HYPERLINK("https://www.news-medical.net/news/20261027/Early-exercise-improves-motor-function-in-a-mouse-model-of-DDX3X-syndrome.aspx","Early exercise improves motor function in a mouse model of DDX3X syndrome")</f>
         <v>Early exercise improves motor function in a mouse model of DDX3X syndrome</v>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
-      <c r="C77" s="3" t="str">
+      <c r="C78" s="3" t="str">
         <f>HYPERLINK("https://www.news-medical.net/news/20261027/Autistic-people-show-weaker-brain-responses-to-negative-feedback.aspx","Autistic people show weaker brain responses to negative feedback")</f>
         <v>Autistic people show weaker brain responses to negative feedback</v>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-27</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t xml:space="preserve">The Transmitter</t>
         </is>
       </c>
-      <c r="C78" s="3" t="str">
+      <c r="C79" s="3" t="str">
         <f>HYPERLINK("https://www.thetransmitter.org/spectrum/behavioral-phenomics-in-zebrafish-and-more/","Behavioral phenomics in zebrafish; and more")</f>
         <v>Behavioral phenomics in zebrafish; and more</v>
       </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-23</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t xml:space="preserve">ScienceDaily</t>
         </is>
       </c>
-      <c r="C79" s="3" t="str">
+      <c r="C80" s="3" t="str">
         <f>HYPERLINK("https://www.sciencedaily.com/releases/2026/10/261022081304.htm","Scientists discover a hidden messaging system deep inside the brain")</f>
         <v>Scientists discover a hidden messaging system deep inside the brain</v>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t xml:space="preserve">ScienceDaily</t>
         </is>
       </c>
-      <c r="C80" s="3" t="str">
+      <c r="C81" s="3" t="str">
         <f>HYPERLINK("https://www.sciencedaily.com/releases/2026/10/261021231235.htm","Scientists discover a surprising secret behind the human brain’s wrinkles")</f>
         <v>Scientists discover a surprising secret behind the human brain’s wrinkles</v>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t xml:space="preserve">News-Medical</t>
         </is>
       </c>
-      <c r="C81" s="3" t="str">
+      <c r="C82" s="3" t="str">
         <f>HYPERLINK("https://www.news-medical.net/news/20261022/Depression-profile-linked-to-disrupted-sleep-and-poorer-treatment-responses.aspx","Depression profile linked to disrupted sleep and poorer treatment responses")</f>
         <v>Depression profile linked to disrupted sleep and poorer treatment responses</v>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-22</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t xml:space="preserve">The Transmitter</t>
         </is>
       </c>
-      <c r="C82" s="3" t="str">
+      <c r="C83" s="3" t="str">
         <f>HYPERLINK("https://www.thetransmitter.org/spectrum/prevalence-of-profound-autism-declines-with-new-definition/","Prevalence of profound autism declines with new definition")</f>
         <v>Prevalence of profound autism declines with new definition</v>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="83"/>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">TRACKED AUTHORS</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t xml:space="preserve">no new papers in the last 7 days (the Author papers sheet lists the 25 most recent)</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t xml:space="preserve">None of the 6 tracked authors published in this window.</t>
         </is>
       </c>
     </row>
-    <row r="86"/>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="87"/>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">CONTENTS</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
+      <c r="B88" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Rows</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
+      <c r="C88" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Window used</t>
         </is>
       </c>
-      <c r="D87" s="1" t="inlineStr">
+      <c r="D88" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Counts when</t>
         </is>
       </c>
-      <c r="E87" s="1" t="inlineStr">
+      <c r="E88" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Store refreshed</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Publications</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">last 7 days (2026-10-21 to 2026-10-28)</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">publication date or the run that added it</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">NIH grants</t>
+          <t xml:space="preserve">Publications</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t xml:space="preserve">434</t>
+          <t xml:space="preserve">40</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">last 90 days (2026-07-30 to 2026-10-28)</t>
+          <t xml:space="preserve">last 7 days (2026-10-21 to 2026-10-28)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">notice of award date</t>
+          <t xml:space="preserve">publication date or the run that added it</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25T21:15:41</t>
+          <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clinical trials</t>
+          <t xml:space="preserve">NIH grants</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve">434</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">last 30 days (2026-09-28 to 2026-10-28)</t>
+          <t xml:space="preserve">last 90 days (2026-07-30 to 2026-10-28)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t xml:space="preserve">ClinicalTrials.gov last-update date</t>
+          <t xml:space="preserve">notice of award date</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25T21:15:49</t>
+          <t xml:space="preserve">2026-10-25T21:15:41</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patents</t>
+          <t xml:space="preserve">Clinical trials</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">75</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">last 90 days (2026-07-30 to 2026-10-28)</t>
+          <t xml:space="preserve">last 30 days (2026-09-28 to 2026-10-28)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">publication or grant date</t>
+          <t xml:space="preserve">ClinicalTrials.gov last-update date</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-25T21:16:13</t>
+          <t xml:space="preserve">2026-10-25T21:15:49</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Press &amp; media</t>
+          <t xml:space="preserve">Patents</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">last 7 days (2026-10-21 to 2026-10-28)</t>
+          <t xml:space="preserve">last 90 days (2026-07-30 to 2026-10-28)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">release date</t>
+          <t xml:space="preserve">publication or grant date</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-28T02:20:55</t>
+          <t xml:space="preserve">2026-10-25T21:16:13</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Author papers</t>
+          <t xml:space="preserve">Press &amp; media</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">nothing in the last 7 days — the 25 most recent instead</t>
+          <t xml:space="preserve">last 7 days (2026-10-21 to 2026-10-28)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">first seen by the tracker, or publication date</t>
+          <t xml:space="preserve">release date</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-10-24</t>
+          <t xml:space="preserve">2026-10-28T02:20:55</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t xml:space="preserve">Author papers</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nothing in the last 7 days — the 25 most recent instead</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">first seen by the tracker, or publication date</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tracked authors</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B95" t="inlineStr">
         <is>
           <t xml:space="preserve">6</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t xml:space="preserve">roster (always complete)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t xml:space="preserve">roster (always complete)</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-24</t>
         </is>
       </c>
     </row>
-    <row r="95"/>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="96"/>
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t xml:space="preserve">Source</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t xml:space="preserve">Autism Research Network Atlas</t>
         </is>

--- a/atlas-weekly.xlsx
+++ b/atlas-weekly.xlsx
@@ -113,7 +113,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Window: 2026-10-21 to 2026-10-28 (last 7 days) · generated 2026-10-28T11:12 · library refreshed 2026-10-24</t>
+          <t xml:space="preserve">Window: 2026-10-21 to 2026-10-28 (last 7 days) · generated 2026-10-28T11:21 · library refreshed 2026-10-24</t>
         </is>
       </c>
     </row>
